--- a/data/wealthcommand.xlsx
+++ b/data/wealthcommand.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovannini.eduardogmail.com/Documents/GitHub/Personal_Finance/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC58387-CA04-0545-A999-70D5144560B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A305D8FD-5D89-AB4F-A548-2B429AEFA9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25680" yWindow="780" windowWidth="25360" windowHeight="27860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44800" yWindow="620" windowWidth="51200" windowHeight="20980" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00 COMMAND CENTER" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 CAPITAL FLOWS'!$B$14:$I$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'05 LIFESTYLE'!$B$33:$G$102</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3479,58 +3479,58 @@
     <xf numFmtId="169" fontId="35" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3541,20 +3541,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="16" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="17" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4675,102 +4675,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="157"/>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
+      <c r="A1" s="152"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
     </row>
     <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="157"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
+      <c r="A2" s="152"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
     </row>
     <row r="3" spans="1:15" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="159" t="s">
+      <c r="B4" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="153"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="156"/>
+      <c r="M4" s="156"/>
+      <c r="N4" s="154"/>
     </row>
     <row r="5" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D5" s="154" t="s">
+      <c r="D5" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="J5" s="154" t="s">
+      <c r="E5" s="154"/>
+      <c r="J5" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="153"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
     </row>
     <row r="6" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D6" s="156" t="str">
+      <c r="D6" s="161" t="str">
         <f>CALC!E162</f>
         <v>R$ 23196,9000</v>
       </c>
-      <c r="E6" s="153"/>
-      <c r="J6" s="158" t="str">
+      <c r="E6" s="154"/>
+      <c r="J6" s="159" t="str">
         <f>CALC!E175</f>
         <v>R$ 4389,6000</v>
       </c>
-      <c r="K6" s="153"/>
-      <c r="L6" s="157"/>
-      <c r="M6" s="157"/>
+      <c r="K6" s="154"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
     </row>
     <row r="8" spans="1:15" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:15" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:15" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:15" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="159" t="s">
+      <c r="B12" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="152"/>
-      <c r="G12" s="152"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="152"/>
-      <c r="K12" s="152"/>
-      <c r="L12" s="152"/>
-      <c r="M12" s="153"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="154"/>
     </row>
     <row r="13" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="133" t="s">
@@ -4788,52 +4788,52 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="161" t="str">
+      <c r="B14" s="158" t="str">
         <f>CALC!E170</f>
         <v>R$ 37245,76000</v>
       </c>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="152"/>
-      <c r="H14" s="152"/>
-      <c r="I14" s="152"/>
-      <c r="J14" s="152"/>
-      <c r="K14" s="152"/>
-      <c r="L14" s="152"/>
-      <c r="M14" s="152"/>
-      <c r="N14" s="153"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="156"/>
+      <c r="J14" s="156"/>
+      <c r="K14" s="156"/>
+      <c r="L14" s="156"/>
+      <c r="M14" s="156"/>
+      <c r="N14" s="154"/>
     </row>
     <row r="15" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="157"/>
-      <c r="G15" s="157"/>
-      <c r="H15" s="157"/>
-      <c r="I15" s="157"/>
-      <c r="J15" s="157"/>
-      <c r="K15" s="157"/>
-      <c r="L15" s="157"/>
-      <c r="M15" s="157"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="152"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="152"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="152"/>
+      <c r="J15" s="152"/>
+      <c r="K15" s="152"/>
+      <c r="L15" s="152"/>
+      <c r="M15" s="152"/>
     </row>
     <row r="16" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="159" t="s">
+      <c r="B16" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="157"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="157"/>
-      <c r="H16" s="152"/>
-      <c r="I16" s="157"/>
-      <c r="J16" s="152"/>
-      <c r="K16" s="157"/>
-      <c r="L16" s="152"/>
-      <c r="M16" s="157"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="156"/>
+      <c r="K16" s="152"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="152"/>
     </row>
     <row r="17" spans="2:14" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="136" t="s">
@@ -4873,35 +4873,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="157"/>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
-      <c r="G19" s="157"/>
-      <c r="H19" s="157"/>
-      <c r="I19" s="157"/>
-      <c r="J19" s="157"/>
-      <c r="K19" s="157"/>
-      <c r="L19" s="157"/>
-      <c r="M19" s="157"/>
-      <c r="N19" s="157"/>
+      <c r="B19" s="152"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="152"/>
+      <c r="I19" s="152"/>
+      <c r="J19" s="152"/>
+      <c r="K19" s="152"/>
+      <c r="L19" s="152"/>
+      <c r="M19" s="152"/>
+      <c r="N19" s="152"/>
     </row>
     <row r="20" spans="2:14" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="159" t="s">
+      <c r="B20" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="152"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="152"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="152"/>
-      <c r="M20" s="153"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="156"/>
+      <c r="E20" s="156"/>
+      <c r="F20" s="156"/>
+      <c r="G20" s="156"/>
+      <c r="H20" s="156"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="156"/>
+      <c r="K20" s="156"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="154"/>
     </row>
     <row r="21" spans="2:14" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="139" t="s">
@@ -4936,12 +4936,12 @@
       <c r="D22" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="155" t="s">
+      <c r="E22" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="152"/>
-      <c r="G22" s="152"/>
-      <c r="H22" s="153"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="156"/>
+      <c r="H22" s="154"/>
       <c r="I22" s="142" t="s">
         <v>22</v>
       </c>
@@ -4959,12 +4959,12 @@
       <c r="D23" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="160" t="s">
+      <c r="E23" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="153"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="154"/>
       <c r="I23" s="145" t="s">
         <v>28</v>
       </c>
@@ -4982,12 +4982,12 @@
       <c r="D24" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="160" t="s">
+      <c r="E24" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="152"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="153"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="156"/>
+      <c r="H24" s="154"/>
       <c r="I24" s="145" t="s">
         <v>28</v>
       </c>
@@ -5005,12 +5005,12 @@
       <c r="D25" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="151" t="s">
+      <c r="E25" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="152"/>
-      <c r="G25" s="152"/>
-      <c r="H25" s="153"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="156"/>
+      <c r="H25" s="154"/>
       <c r="I25" s="148">
         <v>23196.9</v>
       </c>
@@ -5028,12 +5028,12 @@
       <c r="D26" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="151" t="s">
+      <c r="E26" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="153"/>
+      <c r="F26" s="156"/>
+      <c r="G26" s="156"/>
+      <c r="H26" s="154"/>
       <c r="I26" s="148">
         <v>6455.1</v>
       </c>
@@ -5051,12 +5051,12 @@
       <c r="D27" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="155" t="s">
+      <c r="E27" s="157" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="153"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="156"/>
+      <c r="H27" s="154"/>
       <c r="I27" s="150">
         <v>6624.3600000000006</v>
       </c>
@@ -5074,12 +5074,12 @@
       <c r="D28" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="155" t="s">
+      <c r="E28" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="152"/>
-      <c r="G28" s="152"/>
-      <c r="H28" s="153"/>
+      <c r="F28" s="156"/>
+      <c r="G28" s="156"/>
+      <c r="H28" s="154"/>
       <c r="I28" s="150">
         <v>9036.83</v>
       </c>
@@ -5097,12 +5097,12 @@
       <c r="D29" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="155" t="s">
+      <c r="E29" s="157" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="153"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="156"/>
+      <c r="H29" s="154"/>
       <c r="I29" s="150">
         <v>31570.45</v>
       </c>
@@ -5111,23 +5111,36 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="162" t="s">
+      <c r="B31" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="157"/>
-      <c r="M31" s="157"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="152"/>
+      <c r="H31" s="152"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="152"/>
+      <c r="K31" s="152"/>
+      <c r="L31" s="152"/>
+      <c r="M31" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="B20:M20"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="B31:M31"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H15:I15"/>
@@ -5144,19 +5157,6 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="B4:N4"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="B20:M20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5175,43 +5175,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="166" t="s">
+      <c r="B1" s="173" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="170" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
     </row>
     <row r="4" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="153"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+      <c r="J4" s="154"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="53" t="s">
@@ -5326,27 +5326,27 @@
       <c r="B12" s="167" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="152"/>
-      <c r="G12" s="152"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="153"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="154"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="C63" s="152"/>
-      <c r="D63" s="152"/>
-      <c r="E63" s="152"/>
-      <c r="F63" s="152"/>
-      <c r="G63" s="152"/>
-      <c r="H63" s="152"/>
-      <c r="I63" s="152"/>
-      <c r="J63" s="153"/>
+      <c r="C63" s="156"/>
+      <c r="D63" s="156"/>
+      <c r="E63" s="156"/>
+      <c r="F63" s="156"/>
+      <c r="G63" s="156"/>
+      <c r="H63" s="156"/>
+      <c r="I63" s="156"/>
+      <c r="J63" s="154"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="53" t="s">
@@ -5484,14 +5484,14 @@
       <c r="B73" s="167" t="s">
         <v>85</v>
       </c>
-      <c r="C73" s="152"/>
-      <c r="D73" s="152"/>
-      <c r="E73" s="152"/>
-      <c r="F73" s="152"/>
-      <c r="G73" s="152"/>
-      <c r="H73" s="152"/>
-      <c r="I73" s="152"/>
-      <c r="J73" s="153"/>
+      <c r="C73" s="156"/>
+      <c r="D73" s="156"/>
+      <c r="E73" s="156"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="156"/>
+      <c r="H73" s="156"/>
+      <c r="I73" s="156"/>
+      <c r="J73" s="154"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B74" s="53" t="s">
@@ -5616,14 +5616,14 @@
       <c r="B82" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="C82" s="152"/>
-      <c r="D82" s="152"/>
-      <c r="E82" s="152"/>
-      <c r="F82" s="152"/>
-      <c r="G82" s="152"/>
-      <c r="H82" s="152"/>
-      <c r="I82" s="152"/>
-      <c r="J82" s="153"/>
+      <c r="C82" s="156"/>
+      <c r="D82" s="156"/>
+      <c r="E82" s="156"/>
+      <c r="F82" s="156"/>
+      <c r="G82" s="156"/>
+      <c r="H82" s="156"/>
+      <c r="I82" s="156"/>
+      <c r="J82" s="154"/>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B83" s="53" t="s">
@@ -5869,14 +5869,14 @@
       <c r="B96" s="167" t="s">
         <v>112</v>
       </c>
-      <c r="C96" s="152"/>
-      <c r="D96" s="152"/>
-      <c r="E96" s="152"/>
-      <c r="F96" s="152"/>
-      <c r="G96" s="152"/>
-      <c r="H96" s="152"/>
-      <c r="I96" s="152"/>
-      <c r="J96" s="153"/>
+      <c r="C96" s="156"/>
+      <c r="D96" s="156"/>
+      <c r="E96" s="156"/>
+      <c r="F96" s="156"/>
+      <c r="G96" s="156"/>
+      <c r="H96" s="156"/>
+      <c r="I96" s="156"/>
+      <c r="J96" s="154"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B97" s="53" t="s">
@@ -6295,10 +6295,10 @@
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B114" s="174" t="s">
+      <c r="B114" s="165" t="s">
         <v>165</v>
       </c>
-      <c r="C114" s="153"/>
+      <c r="C114" s="154"/>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B115" s="94" t="s">
@@ -6348,14 +6348,14 @@
       <c r="B121" s="167" t="s">
         <v>167</v>
       </c>
-      <c r="C121" s="152"/>
-      <c r="D121" s="152"/>
-      <c r="E121" s="152"/>
-      <c r="F121" s="152"/>
-      <c r="G121" s="152"/>
-      <c r="H121" s="152"/>
-      <c r="I121" s="152"/>
-      <c r="J121" s="153"/>
+      <c r="C121" s="156"/>
+      <c r="D121" s="156"/>
+      <c r="E121" s="156"/>
+      <c r="F121" s="156"/>
+      <c r="G121" s="156"/>
+      <c r="H121" s="156"/>
+      <c r="I121" s="156"/>
+      <c r="J121" s="154"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B122" s="53" t="s">
@@ -6498,121 +6498,121 @@
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B139" s="163" t="s">
+      <c r="B139" s="169" t="s">
         <v>191</v>
       </c>
-      <c r="C139" s="157"/>
-      <c r="D139" s="157"/>
-      <c r="E139" s="157"/>
-      <c r="F139" s="157"/>
-      <c r="G139" s="157"/>
-      <c r="H139" s="157"/>
-      <c r="I139" s="157"/>
-      <c r="J139" s="157"/>
+      <c r="C139" s="152"/>
+      <c r="D139" s="152"/>
+      <c r="E139" s="152"/>
+      <c r="F139" s="152"/>
+      <c r="G139" s="152"/>
+      <c r="H139" s="152"/>
+      <c r="I139" s="152"/>
+      <c r="J139" s="152"/>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B140" s="164" t="s">
+      <c r="B140" s="166" t="s">
         <v>192</v>
       </c>
-      <c r="C140" s="157"/>
-      <c r="D140" s="157"/>
-      <c r="E140" s="157"/>
-      <c r="F140" s="157"/>
-      <c r="G140" s="157"/>
-      <c r="H140" s="157"/>
-      <c r="I140" s="157"/>
-      <c r="J140" s="157"/>
+      <c r="C140" s="152"/>
+      <c r="D140" s="152"/>
+      <c r="E140" s="152"/>
+      <c r="F140" s="152"/>
+      <c r="G140" s="152"/>
+      <c r="H140" s="152"/>
+      <c r="I140" s="152"/>
+      <c r="J140" s="152"/>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B148" s="164" t="s">
+      <c r="B148" s="166" t="s">
         <v>193</v>
       </c>
-      <c r="C148" s="157"/>
-      <c r="D148" s="157"/>
-      <c r="E148" s="157"/>
-      <c r="F148" s="157"/>
-      <c r="G148" s="157"/>
-      <c r="H148" s="157"/>
-      <c r="I148" s="157"/>
-      <c r="J148" s="157"/>
+      <c r="C148" s="152"/>
+      <c r="D148" s="152"/>
+      <c r="E148" s="152"/>
+      <c r="F148" s="152"/>
+      <c r="G148" s="152"/>
+      <c r="H148" s="152"/>
+      <c r="I148" s="152"/>
+      <c r="J148" s="152"/>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B149" s="164" t="s">
+      <c r="B149" s="166" t="s">
         <v>194</v>
       </c>
-      <c r="C149" s="157"/>
-      <c r="D149" s="157"/>
-      <c r="E149" s="157"/>
-      <c r="F149" s="157"/>
-      <c r="G149" s="157"/>
-      <c r="H149" s="157"/>
-      <c r="I149" s="157"/>
-      <c r="J149" s="157"/>
+      <c r="C149" s="152"/>
+      <c r="D149" s="152"/>
+      <c r="E149" s="152"/>
+      <c r="F149" s="152"/>
+      <c r="G149" s="152"/>
+      <c r="H149" s="152"/>
+      <c r="I149" s="152"/>
+      <c r="J149" s="152"/>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B150" s="164" t="s">
+      <c r="B150" s="166" t="s">
         <v>195</v>
       </c>
-      <c r="C150" s="157"/>
-      <c r="D150" s="157"/>
-      <c r="E150" s="157"/>
-      <c r="F150" s="157"/>
-      <c r="G150" s="157"/>
-      <c r="H150" s="157"/>
-      <c r="I150" s="157"/>
-      <c r="J150" s="157"/>
+      <c r="C150" s="152"/>
+      <c r="D150" s="152"/>
+      <c r="E150" s="152"/>
+      <c r="F150" s="152"/>
+      <c r="G150" s="152"/>
+      <c r="H150" s="152"/>
+      <c r="I150" s="152"/>
+      <c r="J150" s="152"/>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B151" s="164" t="s">
+      <c r="B151" s="166" t="s">
         <v>196</v>
       </c>
-      <c r="C151" s="157"/>
-      <c r="D151" s="157"/>
-      <c r="E151" s="157"/>
-      <c r="F151" s="157"/>
-      <c r="G151" s="157"/>
-      <c r="H151" s="157"/>
-      <c r="I151" s="157"/>
-      <c r="J151" s="157"/>
+      <c r="C151" s="152"/>
+      <c r="D151" s="152"/>
+      <c r="E151" s="152"/>
+      <c r="F151" s="152"/>
+      <c r="G151" s="152"/>
+      <c r="H151" s="152"/>
+      <c r="I151" s="152"/>
+      <c r="J151" s="152"/>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B152" s="164" t="s">
+      <c r="B152" s="166" t="s">
         <v>197</v>
       </c>
-      <c r="C152" s="157"/>
-      <c r="D152" s="157"/>
-      <c r="E152" s="157"/>
-      <c r="F152" s="157"/>
-      <c r="G152" s="157"/>
-      <c r="H152" s="157"/>
-      <c r="I152" s="157"/>
-      <c r="J152" s="157"/>
+      <c r="C152" s="152"/>
+      <c r="D152" s="152"/>
+      <c r="E152" s="152"/>
+      <c r="F152" s="152"/>
+      <c r="G152" s="152"/>
+      <c r="H152" s="152"/>
+      <c r="I152" s="152"/>
+      <c r="J152" s="152"/>
     </row>
     <row r="157" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B157" s="167" t="s">
         <v>198</v>
       </c>
-      <c r="C157" s="152"/>
-      <c r="D157" s="152"/>
-      <c r="E157" s="152"/>
-      <c r="F157" s="152"/>
-      <c r="G157" s="152"/>
-      <c r="H157" s="152"/>
-      <c r="I157" s="152"/>
-      <c r="J157" s="153"/>
+      <c r="C157" s="156"/>
+      <c r="D157" s="156"/>
+      <c r="E157" s="156"/>
+      <c r="F157" s="156"/>
+      <c r="G157" s="156"/>
+      <c r="H157" s="156"/>
+      <c r="I157" s="156"/>
+      <c r="J157" s="154"/>
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B158" s="163" t="s">
+      <c r="B158" s="169" t="s">
         <v>199</v>
       </c>
-      <c r="C158" s="157"/>
-      <c r="D158" s="157"/>
-      <c r="E158" s="157"/>
-      <c r="F158" s="157"/>
-      <c r="G158" s="157"/>
-      <c r="H158" s="157"/>
-      <c r="I158" s="157"/>
-      <c r="J158" s="157"/>
+      <c r="C158" s="152"/>
+      <c r="D158" s="152"/>
+      <c r="E158" s="152"/>
+      <c r="F158" s="152"/>
+      <c r="G158" s="152"/>
+      <c r="H158" s="152"/>
+      <c r="I158" s="152"/>
+      <c r="J158" s="152"/>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B160" s="53" t="s">
@@ -6791,14 +6791,14 @@
       <c r="B177" s="167" t="s">
         <v>217</v>
       </c>
-      <c r="C177" s="152"/>
-      <c r="D177" s="152"/>
-      <c r="E177" s="152"/>
-      <c r="F177" s="152"/>
-      <c r="G177" s="152"/>
-      <c r="H177" s="152"/>
-      <c r="I177" s="152"/>
-      <c r="J177" s="153"/>
+      <c r="C177" s="156"/>
+      <c r="D177" s="156"/>
+      <c r="E177" s="156"/>
+      <c r="F177" s="156"/>
+      <c r="G177" s="156"/>
+      <c r="H177" s="156"/>
+      <c r="I177" s="156"/>
+      <c r="J177" s="154"/>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B178" s="53" t="s">
@@ -6971,274 +6971,274 @@
       <c r="B187" s="167" t="s">
         <v>228</v>
       </c>
-      <c r="C187" s="152"/>
-      <c r="D187" s="152"/>
-      <c r="E187" s="152"/>
-      <c r="F187" s="152"/>
-      <c r="G187" s="152"/>
-      <c r="H187" s="152"/>
-      <c r="I187" s="152"/>
-      <c r="J187" s="153"/>
+      <c r="C187" s="156"/>
+      <c r="D187" s="156"/>
+      <c r="E187" s="156"/>
+      <c r="F187" s="156"/>
+      <c r="G187" s="156"/>
+      <c r="H187" s="156"/>
+      <c r="I187" s="156"/>
+      <c r="J187" s="154"/>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B188" s="163" t="s">
+      <c r="B188" s="169" t="s">
         <v>229</v>
       </c>
-      <c r="C188" s="157"/>
-      <c r="D188" s="157"/>
-      <c r="E188" s="157"/>
-      <c r="F188" s="157"/>
-      <c r="G188" s="157"/>
-      <c r="H188" s="157"/>
-      <c r="I188" s="157"/>
-      <c r="J188" s="157"/>
+      <c r="C188" s="152"/>
+      <c r="D188" s="152"/>
+      <c r="E188" s="152"/>
+      <c r="F188" s="152"/>
+      <c r="G188" s="152"/>
+      <c r="H188" s="152"/>
+      <c r="I188" s="152"/>
+      <c r="J188" s="152"/>
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B189" s="163" t="s">
+      <c r="B189" s="169" t="s">
         <v>230</v>
       </c>
-      <c r="C189" s="157"/>
-      <c r="D189" s="157"/>
-      <c r="E189" s="157"/>
-      <c r="F189" s="157"/>
-      <c r="G189" s="157"/>
-      <c r="H189" s="157"/>
-      <c r="I189" s="157"/>
-      <c r="J189" s="157"/>
+      <c r="C189" s="152"/>
+      <c r="D189" s="152"/>
+      <c r="E189" s="152"/>
+      <c r="F189" s="152"/>
+      <c r="G189" s="152"/>
+      <c r="H189" s="152"/>
+      <c r="I189" s="152"/>
+      <c r="J189" s="152"/>
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B190" s="163" t="s">
+      <c r="B190" s="169" t="s">
         <v>231</v>
       </c>
-      <c r="C190" s="157"/>
-      <c r="D190" s="157"/>
-      <c r="E190" s="157"/>
-      <c r="F190" s="157"/>
-      <c r="G190" s="157"/>
-      <c r="H190" s="157"/>
-      <c r="I190" s="157"/>
-      <c r="J190" s="157"/>
+      <c r="C190" s="152"/>
+      <c r="D190" s="152"/>
+      <c r="E190" s="152"/>
+      <c r="F190" s="152"/>
+      <c r="G190" s="152"/>
+      <c r="H190" s="152"/>
+      <c r="I190" s="152"/>
+      <c r="J190" s="152"/>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B191" s="169"/>
-      <c r="C191" s="157"/>
-      <c r="D191" s="157"/>
-      <c r="E191" s="157"/>
-      <c r="F191" s="157"/>
-      <c r="G191" s="157"/>
-      <c r="H191" s="157"/>
-      <c r="I191" s="157"/>
-      <c r="J191" s="157"/>
+      <c r="B191" s="174"/>
+      <c r="C191" s="152"/>
+      <c r="D191" s="152"/>
+      <c r="E191" s="152"/>
+      <c r="F191" s="152"/>
+      <c r="G191" s="152"/>
+      <c r="H191" s="152"/>
+      <c r="I191" s="152"/>
+      <c r="J191" s="152"/>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B192" s="168" t="s">
+      <c r="B192" s="164" t="s">
         <v>232</v>
       </c>
-      <c r="C192" s="157"/>
-      <c r="D192" s="157"/>
-      <c r="E192" s="157"/>
-      <c r="F192" s="157"/>
-      <c r="G192" s="157"/>
-      <c r="H192" s="157"/>
-      <c r="I192" s="157"/>
-      <c r="J192" s="157"/>
+      <c r="C192" s="152"/>
+      <c r="D192" s="152"/>
+      <c r="E192" s="152"/>
+      <c r="F192" s="152"/>
+      <c r="G192" s="152"/>
+      <c r="H192" s="152"/>
+      <c r="I192" s="152"/>
+      <c r="J192" s="152"/>
     </row>
     <row r="194" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B194" s="165" t="s">
+      <c r="B194" s="163" t="s">
         <v>233</v>
       </c>
-      <c r="C194" s="157"/>
-      <c r="D194" s="157"/>
-      <c r="E194" s="157"/>
-      <c r="F194" s="157"/>
-      <c r="G194" s="157"/>
-      <c r="H194" s="157"/>
-      <c r="I194" s="157"/>
-      <c r="J194" s="157"/>
+      <c r="C194" s="152"/>
+      <c r="D194" s="152"/>
+      <c r="E194" s="152"/>
+      <c r="F194" s="152"/>
+      <c r="G194" s="152"/>
+      <c r="H194" s="152"/>
+      <c r="I194" s="152"/>
+      <c r="J194" s="152"/>
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B202" s="165" t="s">
+      <c r="B202" s="163" t="s">
         <v>234</v>
       </c>
-      <c r="C202" s="157"/>
-      <c r="D202" s="157"/>
-      <c r="E202" s="157"/>
-      <c r="F202" s="157"/>
-      <c r="G202" s="157"/>
-      <c r="H202" s="157"/>
-      <c r="I202" s="157"/>
-      <c r="J202" s="157"/>
+      <c r="C202" s="152"/>
+      <c r="D202" s="152"/>
+      <c r="E202" s="152"/>
+      <c r="F202" s="152"/>
+      <c r="G202" s="152"/>
+      <c r="H202" s="152"/>
+      <c r="I202" s="152"/>
+      <c r="J202" s="152"/>
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B203" s="165" t="s">
+      <c r="B203" s="163" t="s">
         <v>235</v>
       </c>
-      <c r="C203" s="157"/>
-      <c r="D203" s="157"/>
-      <c r="E203" s="157"/>
-      <c r="F203" s="157"/>
-      <c r="G203" s="157"/>
-      <c r="H203" s="157"/>
-      <c r="I203" s="157"/>
-      <c r="J203" s="157"/>
+      <c r="C203" s="152"/>
+      <c r="D203" s="152"/>
+      <c r="E203" s="152"/>
+      <c r="F203" s="152"/>
+      <c r="G203" s="152"/>
+      <c r="H203" s="152"/>
+      <c r="I203" s="152"/>
+      <c r="J203" s="152"/>
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B205" s="165" t="s">
+      <c r="B205" s="163" t="s">
         <v>236</v>
       </c>
-      <c r="C205" s="157"/>
-      <c r="D205" s="157"/>
-      <c r="E205" s="157"/>
-      <c r="F205" s="157"/>
-      <c r="G205" s="157"/>
-      <c r="H205" s="157"/>
-      <c r="I205" s="157"/>
-      <c r="J205" s="157"/>
+      <c r="C205" s="152"/>
+      <c r="D205" s="152"/>
+      <c r="E205" s="152"/>
+      <c r="F205" s="152"/>
+      <c r="G205" s="152"/>
+      <c r="H205" s="152"/>
+      <c r="I205" s="152"/>
+      <c r="J205" s="152"/>
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B206" s="165" t="s">
+      <c r="B206" s="163" t="s">
         <v>237</v>
       </c>
-      <c r="C206" s="157"/>
-      <c r="D206" s="157"/>
-      <c r="E206" s="157"/>
-      <c r="F206" s="157"/>
-      <c r="G206" s="157"/>
-      <c r="H206" s="157"/>
-      <c r="I206" s="157"/>
-      <c r="J206" s="157"/>
+      <c r="C206" s="152"/>
+      <c r="D206" s="152"/>
+      <c r="E206" s="152"/>
+      <c r="F206" s="152"/>
+      <c r="G206" s="152"/>
+      <c r="H206" s="152"/>
+      <c r="I206" s="152"/>
+      <c r="J206" s="152"/>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B207" s="165" t="s">
+      <c r="B207" s="163" t="s">
         <v>238</v>
       </c>
-      <c r="C207" s="157"/>
-      <c r="D207" s="157"/>
-      <c r="E207" s="157"/>
-      <c r="F207" s="157"/>
-      <c r="G207" s="157"/>
-      <c r="H207" s="157"/>
-      <c r="I207" s="157"/>
-      <c r="J207" s="157"/>
+      <c r="C207" s="152"/>
+      <c r="D207" s="152"/>
+      <c r="E207" s="152"/>
+      <c r="F207" s="152"/>
+      <c r="G207" s="152"/>
+      <c r="H207" s="152"/>
+      <c r="I207" s="152"/>
+      <c r="J207" s="152"/>
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B209" s="168" t="s">
+      <c r="B209" s="164" t="s">
         <v>239</v>
       </c>
-      <c r="C209" s="157"/>
-      <c r="D209" s="157"/>
-      <c r="E209" s="157"/>
-      <c r="F209" s="157"/>
-      <c r="G209" s="157"/>
-      <c r="H209" s="157"/>
-      <c r="I209" s="157"/>
-      <c r="J209" s="157"/>
+      <c r="C209" s="152"/>
+      <c r="D209" s="152"/>
+      <c r="E209" s="152"/>
+      <c r="F209" s="152"/>
+      <c r="G209" s="152"/>
+      <c r="H209" s="152"/>
+      <c r="I209" s="152"/>
+      <c r="J209" s="152"/>
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B210" s="165" t="s">
+      <c r="B210" s="163" t="s">
         <v>240</v>
       </c>
-      <c r="C210" s="157"/>
-      <c r="D210" s="157"/>
-      <c r="E210" s="157"/>
-      <c r="F210" s="157"/>
-      <c r="G210" s="157"/>
-      <c r="H210" s="157"/>
-      <c r="I210" s="157"/>
-      <c r="J210" s="157"/>
+      <c r="C210" s="152"/>
+      <c r="D210" s="152"/>
+      <c r="E210" s="152"/>
+      <c r="F210" s="152"/>
+      <c r="G210" s="152"/>
+      <c r="H210" s="152"/>
+      <c r="I210" s="152"/>
+      <c r="J210" s="152"/>
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B211" s="165" t="s">
+      <c r="B211" s="163" t="s">
         <v>241</v>
       </c>
-      <c r="C211" s="157"/>
-      <c r="D211" s="157"/>
-      <c r="E211" s="157"/>
-      <c r="F211" s="157"/>
-      <c r="G211" s="157"/>
-      <c r="H211" s="157"/>
-      <c r="I211" s="157"/>
-      <c r="J211" s="157"/>
+      <c r="C211" s="152"/>
+      <c r="D211" s="152"/>
+      <c r="E211" s="152"/>
+      <c r="F211" s="152"/>
+      <c r="G211" s="152"/>
+      <c r="H211" s="152"/>
+      <c r="I211" s="152"/>
+      <c r="J211" s="152"/>
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B212" s="165" t="s">
+      <c r="B212" s="163" t="s">
         <v>242</v>
       </c>
-      <c r="C212" s="157"/>
-      <c r="D212" s="157"/>
-      <c r="E212" s="157"/>
-      <c r="F212" s="157"/>
-      <c r="G212" s="157"/>
-      <c r="H212" s="157"/>
-      <c r="I212" s="157"/>
-      <c r="J212" s="157"/>
+      <c r="C212" s="152"/>
+      <c r="D212" s="152"/>
+      <c r="E212" s="152"/>
+      <c r="F212" s="152"/>
+      <c r="G212" s="152"/>
+      <c r="H212" s="152"/>
+      <c r="I212" s="152"/>
+      <c r="J212" s="152"/>
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B213" s="165" t="s">
+      <c r="B213" s="163" t="s">
         <v>243</v>
       </c>
-      <c r="C213" s="157"/>
-      <c r="D213" s="157"/>
-      <c r="E213" s="157"/>
-      <c r="F213" s="157"/>
-      <c r="G213" s="157"/>
-      <c r="H213" s="157"/>
-      <c r="I213" s="157"/>
-      <c r="J213" s="157"/>
+      <c r="C213" s="152"/>
+      <c r="D213" s="152"/>
+      <c r="E213" s="152"/>
+      <c r="F213" s="152"/>
+      <c r="G213" s="152"/>
+      <c r="H213" s="152"/>
+      <c r="I213" s="152"/>
+      <c r="J213" s="152"/>
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B214" s="165" t="s">
+      <c r="B214" s="163" t="s">
         <v>244</v>
       </c>
-      <c r="C214" s="157"/>
-      <c r="D214" s="157"/>
-      <c r="E214" s="157"/>
-      <c r="F214" s="157"/>
-      <c r="G214" s="157"/>
-      <c r="H214" s="157"/>
-      <c r="I214" s="157"/>
-      <c r="J214" s="157"/>
+      <c r="C214" s="152"/>
+      <c r="D214" s="152"/>
+      <c r="E214" s="152"/>
+      <c r="F214" s="152"/>
+      <c r="G214" s="152"/>
+      <c r="H214" s="152"/>
+      <c r="I214" s="152"/>
+      <c r="J214" s="152"/>
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B215" s="165" t="s">
+      <c r="B215" s="163" t="s">
         <v>245</v>
       </c>
-      <c r="C215" s="157"/>
-      <c r="D215" s="157"/>
-      <c r="E215" s="157"/>
-      <c r="F215" s="157"/>
-      <c r="G215" s="157"/>
-      <c r="H215" s="157"/>
-      <c r="I215" s="157"/>
-      <c r="J215" s="157"/>
+      <c r="C215" s="152"/>
+      <c r="D215" s="152"/>
+      <c r="E215" s="152"/>
+      <c r="F215" s="152"/>
+      <c r="G215" s="152"/>
+      <c r="H215" s="152"/>
+      <c r="I215" s="152"/>
+      <c r="J215" s="152"/>
     </row>
     <row r="218" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B218" s="167" t="s">
         <v>246</v>
       </c>
-      <c r="C218" s="152"/>
-      <c r="D218" s="152"/>
-      <c r="E218" s="152"/>
-      <c r="F218" s="152"/>
-      <c r="G218" s="152"/>
-      <c r="H218" s="152"/>
-      <c r="I218" s="152"/>
-      <c r="J218" s="152"/>
-      <c r="K218" s="153"/>
+      <c r="C218" s="156"/>
+      <c r="D218" s="156"/>
+      <c r="E218" s="156"/>
+      <c r="F218" s="156"/>
+      <c r="G218" s="156"/>
+      <c r="H218" s="156"/>
+      <c r="I218" s="156"/>
+      <c r="J218" s="156"/>
+      <c r="K218" s="154"/>
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B219" s="163" t="s">
+      <c r="B219" s="169" t="s">
         <v>247</v>
       </c>
-      <c r="C219" s="157"/>
-      <c r="D219" s="157"/>
-      <c r="E219" s="157"/>
-      <c r="F219" s="157"/>
-      <c r="G219" s="157"/>
-      <c r="H219" s="157"/>
-      <c r="I219" s="157"/>
-      <c r="J219" s="157"/>
-      <c r="K219" s="157"/>
+      <c r="C219" s="152"/>
+      <c r="D219" s="152"/>
+      <c r="E219" s="152"/>
+      <c r="F219" s="152"/>
+      <c r="G219" s="152"/>
+      <c r="H219" s="152"/>
+      <c r="I219" s="152"/>
+      <c r="J219" s="152"/>
+      <c r="K219" s="152"/>
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B220" s="109" t="s">
@@ -7359,29 +7359,29 @@
       <c r="B229" s="167" t="s">
         <v>249</v>
       </c>
-      <c r="C229" s="152"/>
-      <c r="D229" s="152"/>
-      <c r="E229" s="152"/>
-      <c r="F229" s="152"/>
-      <c r="G229" s="152"/>
-      <c r="H229" s="152"/>
-      <c r="I229" s="152"/>
-      <c r="J229" s="152"/>
-      <c r="K229" s="153"/>
+      <c r="C229" s="156"/>
+      <c r="D229" s="156"/>
+      <c r="E229" s="156"/>
+      <c r="F229" s="156"/>
+      <c r="G229" s="156"/>
+      <c r="H229" s="156"/>
+      <c r="I229" s="156"/>
+      <c r="J229" s="156"/>
+      <c r="K229" s="154"/>
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B230" s="163" t="s">
+      <c r="B230" s="169" t="s">
         <v>250</v>
       </c>
-      <c r="C230" s="157"/>
-      <c r="D230" s="157"/>
-      <c r="E230" s="157"/>
-      <c r="F230" s="157"/>
-      <c r="G230" s="157"/>
-      <c r="H230" s="157"/>
-      <c r="I230" s="157"/>
-      <c r="J230" s="157"/>
-      <c r="K230" s="157"/>
+      <c r="C230" s="152"/>
+      <c r="D230" s="152"/>
+      <c r="E230" s="152"/>
+      <c r="F230" s="152"/>
+      <c r="G230" s="152"/>
+      <c r="H230" s="152"/>
+      <c r="I230" s="152"/>
+      <c r="J230" s="152"/>
+      <c r="K230" s="152"/>
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B231" s="109" t="s">
@@ -7464,15 +7464,15 @@
       <c r="B241" s="167" t="s">
         <v>260</v>
       </c>
-      <c r="C241" s="152"/>
-      <c r="D241" s="152"/>
-      <c r="E241" s="152"/>
-      <c r="F241" s="152"/>
-      <c r="G241" s="152"/>
-      <c r="H241" s="152"/>
-      <c r="I241" s="152"/>
-      <c r="J241" s="152"/>
-      <c r="K241" s="153"/>
+      <c r="C241" s="156"/>
+      <c r="D241" s="156"/>
+      <c r="E241" s="156"/>
+      <c r="F241" s="156"/>
+      <c r="G241" s="156"/>
+      <c r="H241" s="156"/>
+      <c r="I241" s="156"/>
+      <c r="J241" s="156"/>
+      <c r="K241" s="154"/>
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B242" s="109" t="s">
@@ -7531,144 +7531,144 @@
       </c>
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B250" s="168" t="s">
+      <c r="B250" s="164" t="s">
         <v>262</v>
       </c>
-      <c r="C250" s="157"/>
-      <c r="D250" s="157"/>
-      <c r="E250" s="157"/>
-      <c r="F250" s="157"/>
-      <c r="G250" s="157"/>
-      <c r="H250" s="157"/>
-      <c r="I250" s="157"/>
-      <c r="J250" s="157"/>
-      <c r="K250" s="157"/>
+      <c r="C250" s="152"/>
+      <c r="D250" s="152"/>
+      <c r="E250" s="152"/>
+      <c r="F250" s="152"/>
+      <c r="G250" s="152"/>
+      <c r="H250" s="152"/>
+      <c r="I250" s="152"/>
+      <c r="J250" s="152"/>
+      <c r="K250" s="152"/>
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B251" s="165" t="s">
+      <c r="B251" s="163" t="s">
         <v>263</v>
       </c>
-      <c r="C251" s="157"/>
-      <c r="D251" s="157"/>
-      <c r="E251" s="157"/>
-      <c r="F251" s="157"/>
-      <c r="G251" s="157"/>
-      <c r="H251" s="157"/>
-      <c r="I251" s="157"/>
-      <c r="J251" s="157"/>
-      <c r="K251" s="157"/>
+      <c r="C251" s="152"/>
+      <c r="D251" s="152"/>
+      <c r="E251" s="152"/>
+      <c r="F251" s="152"/>
+      <c r="G251" s="152"/>
+      <c r="H251" s="152"/>
+      <c r="I251" s="152"/>
+      <c r="J251" s="152"/>
+      <c r="K251" s="152"/>
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B252" s="165" t="s">
+      <c r="B252" s="163" t="s">
         <v>264</v>
       </c>
-      <c r="C252" s="157"/>
-      <c r="D252" s="157"/>
-      <c r="E252" s="157"/>
-      <c r="F252" s="157"/>
-      <c r="G252" s="157"/>
-      <c r="H252" s="157"/>
-      <c r="I252" s="157"/>
-      <c r="J252" s="157"/>
-      <c r="K252" s="157"/>
+      <c r="C252" s="152"/>
+      <c r="D252" s="152"/>
+      <c r="E252" s="152"/>
+      <c r="F252" s="152"/>
+      <c r="G252" s="152"/>
+      <c r="H252" s="152"/>
+      <c r="I252" s="152"/>
+      <c r="J252" s="152"/>
+      <c r="K252" s="152"/>
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B253" s="165" t="s">
+      <c r="B253" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="C253" s="157"/>
-      <c r="D253" s="157"/>
-      <c r="E253" s="157"/>
-      <c r="F253" s="157"/>
-      <c r="G253" s="157"/>
-      <c r="H253" s="157"/>
-      <c r="I253" s="157"/>
-      <c r="J253" s="157"/>
-      <c r="K253" s="157"/>
+      <c r="C253" s="152"/>
+      <c r="D253" s="152"/>
+      <c r="E253" s="152"/>
+      <c r="F253" s="152"/>
+      <c r="G253" s="152"/>
+      <c r="H253" s="152"/>
+      <c r="I253" s="152"/>
+      <c r="J253" s="152"/>
+      <c r="K253" s="152"/>
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B254" s="165" t="s">
+      <c r="B254" s="163" t="s">
         <v>266</v>
       </c>
-      <c r="C254" s="157"/>
-      <c r="D254" s="157"/>
-      <c r="E254" s="157"/>
-      <c r="F254" s="157"/>
-      <c r="G254" s="157"/>
-      <c r="H254" s="157"/>
-      <c r="I254" s="157"/>
-      <c r="J254" s="157"/>
-      <c r="K254" s="157"/>
+      <c r="C254" s="152"/>
+      <c r="D254" s="152"/>
+      <c r="E254" s="152"/>
+      <c r="F254" s="152"/>
+      <c r="G254" s="152"/>
+      <c r="H254" s="152"/>
+      <c r="I254" s="152"/>
+      <c r="J254" s="152"/>
+      <c r="K254" s="152"/>
     </row>
     <row r="256" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B256" s="168" t="s">
+      <c r="B256" s="164" t="s">
         <v>267</v>
       </c>
-      <c r="C256" s="157"/>
-      <c r="D256" s="157"/>
-      <c r="E256" s="157"/>
-      <c r="F256" s="157"/>
-      <c r="G256" s="157"/>
-      <c r="H256" s="157"/>
-      <c r="I256" s="157"/>
-      <c r="J256" s="157"/>
-      <c r="K256" s="157"/>
+      <c r="C256" s="152"/>
+      <c r="D256" s="152"/>
+      <c r="E256" s="152"/>
+      <c r="F256" s="152"/>
+      <c r="G256" s="152"/>
+      <c r="H256" s="152"/>
+      <c r="I256" s="152"/>
+      <c r="J256" s="152"/>
+      <c r="K256" s="152"/>
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B257" s="165" t="s">
+      <c r="B257" s="163" t="s">
         <v>268</v>
       </c>
-      <c r="C257" s="157"/>
-      <c r="D257" s="157"/>
-      <c r="E257" s="157"/>
-      <c r="F257" s="157"/>
-      <c r="G257" s="157"/>
-      <c r="H257" s="157"/>
-      <c r="I257" s="157"/>
-      <c r="J257" s="157"/>
-      <c r="K257" s="157"/>
+      <c r="C257" s="152"/>
+      <c r="D257" s="152"/>
+      <c r="E257" s="152"/>
+      <c r="F257" s="152"/>
+      <c r="G257" s="152"/>
+      <c r="H257" s="152"/>
+      <c r="I257" s="152"/>
+      <c r="J257" s="152"/>
+      <c r="K257" s="152"/>
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B259" s="165" t="s">
+      <c r="B259" s="163" t="s">
         <v>269</v>
       </c>
-      <c r="C259" s="157"/>
-      <c r="D259" s="157"/>
-      <c r="E259" s="157"/>
-      <c r="F259" s="157"/>
-      <c r="G259" s="157"/>
-      <c r="H259" s="157"/>
-      <c r="I259" s="157"/>
-      <c r="J259" s="157"/>
-      <c r="K259" s="157"/>
+      <c r="C259" s="152"/>
+      <c r="D259" s="152"/>
+      <c r="E259" s="152"/>
+      <c r="F259" s="152"/>
+      <c r="G259" s="152"/>
+      <c r="H259" s="152"/>
+      <c r="I259" s="152"/>
+      <c r="J259" s="152"/>
+      <c r="K259" s="152"/>
     </row>
     <row r="266" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B266" s="167" t="s">
         <v>270</v>
       </c>
-      <c r="C266" s="152"/>
-      <c r="D266" s="152"/>
-      <c r="E266" s="152"/>
-      <c r="F266" s="152"/>
-      <c r="G266" s="152"/>
-      <c r="H266" s="152"/>
-      <c r="I266" s="152"/>
-      <c r="J266" s="152"/>
-      <c r="K266" s="153"/>
+      <c r="C266" s="156"/>
+      <c r="D266" s="156"/>
+      <c r="E266" s="156"/>
+      <c r="F266" s="156"/>
+      <c r="G266" s="156"/>
+      <c r="H266" s="156"/>
+      <c r="I266" s="156"/>
+      <c r="J266" s="156"/>
+      <c r="K266" s="154"/>
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B267" s="170" t="s">
+      <c r="B267" s="172" t="s">
         <v>271</v>
       </c>
-      <c r="C267" s="152"/>
-      <c r="D267" s="152"/>
-      <c r="E267" s="152"/>
-      <c r="F267" s="152"/>
-      <c r="G267" s="152"/>
-      <c r="H267" s="152"/>
-      <c r="I267" s="152"/>
-      <c r="J267" s="152"/>
-      <c r="K267" s="153"/>
+      <c r="C267" s="156"/>
+      <c r="D267" s="156"/>
+      <c r="E267" s="156"/>
+      <c r="F267" s="156"/>
+      <c r="G267" s="156"/>
+      <c r="H267" s="156"/>
+      <c r="I267" s="156"/>
+      <c r="J267" s="156"/>
+      <c r="K267" s="154"/>
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B268" s="109" t="s">
@@ -7789,15 +7789,15 @@
       <c r="B277" s="167" t="s">
         <v>272</v>
       </c>
-      <c r="C277" s="152"/>
-      <c r="D277" s="152"/>
-      <c r="E277" s="152"/>
-      <c r="F277" s="152"/>
-      <c r="G277" s="152"/>
-      <c r="H277" s="152"/>
-      <c r="I277" s="152"/>
-      <c r="J277" s="152"/>
-      <c r="K277" s="153"/>
+      <c r="C277" s="156"/>
+      <c r="D277" s="156"/>
+      <c r="E277" s="156"/>
+      <c r="F277" s="156"/>
+      <c r="G277" s="156"/>
+      <c r="H277" s="156"/>
+      <c r="I277" s="156"/>
+      <c r="J277" s="156"/>
+      <c r="K277" s="154"/>
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B278" s="109" t="s">
@@ -7873,166 +7873,166 @@
       <c r="B287" s="167" t="s">
         <v>276</v>
       </c>
-      <c r="C287" s="152"/>
-      <c r="D287" s="152"/>
-      <c r="E287" s="152"/>
-      <c r="F287" s="152"/>
-      <c r="G287" s="152"/>
-      <c r="H287" s="152"/>
-      <c r="I287" s="152"/>
-      <c r="J287" s="152"/>
-      <c r="K287" s="153"/>
+      <c r="C287" s="156"/>
+      <c r="D287" s="156"/>
+      <c r="E287" s="156"/>
+      <c r="F287" s="156"/>
+      <c r="G287" s="156"/>
+      <c r="H287" s="156"/>
+      <c r="I287" s="156"/>
+      <c r="J287" s="156"/>
+      <c r="K287" s="154"/>
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B288" s="165" t="s">
+      <c r="B288" s="163" t="s">
         <v>277</v>
       </c>
-      <c r="C288" s="157"/>
-      <c r="D288" s="157"/>
-      <c r="E288" s="157"/>
-      <c r="F288" s="157"/>
-      <c r="G288" s="157"/>
-      <c r="H288" s="157"/>
-      <c r="I288" s="157"/>
-      <c r="J288" s="157"/>
-      <c r="K288" s="157"/>
+      <c r="C288" s="152"/>
+      <c r="D288" s="152"/>
+      <c r="E288" s="152"/>
+      <c r="F288" s="152"/>
+      <c r="G288" s="152"/>
+      <c r="H288" s="152"/>
+      <c r="I288" s="152"/>
+      <c r="J288" s="152"/>
+      <c r="K288" s="152"/>
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B289" s="165" t="s">
+      <c r="B289" s="163" t="s">
         <v>278</v>
       </c>
-      <c r="C289" s="157"/>
-      <c r="D289" s="157"/>
-      <c r="E289" s="157"/>
-      <c r="F289" s="157"/>
-      <c r="G289" s="157"/>
-      <c r="H289" s="157"/>
-      <c r="I289" s="157"/>
-      <c r="J289" s="157"/>
-      <c r="K289" s="157"/>
+      <c r="C289" s="152"/>
+      <c r="D289" s="152"/>
+      <c r="E289" s="152"/>
+      <c r="F289" s="152"/>
+      <c r="G289" s="152"/>
+      <c r="H289" s="152"/>
+      <c r="I289" s="152"/>
+      <c r="J289" s="152"/>
+      <c r="K289" s="152"/>
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B290" s="165" t="s">
+      <c r="B290" s="163" t="s">
         <v>279</v>
       </c>
-      <c r="C290" s="157"/>
-      <c r="D290" s="157"/>
-      <c r="E290" s="157"/>
-      <c r="F290" s="157"/>
-      <c r="G290" s="157"/>
-      <c r="H290" s="157"/>
-      <c r="I290" s="157"/>
-      <c r="J290" s="157"/>
-      <c r="K290" s="157"/>
+      <c r="C290" s="152"/>
+      <c r="D290" s="152"/>
+      <c r="E290" s="152"/>
+      <c r="F290" s="152"/>
+      <c r="G290" s="152"/>
+      <c r="H290" s="152"/>
+      <c r="I290" s="152"/>
+      <c r="J290" s="152"/>
+      <c r="K290" s="152"/>
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B291" s="165" t="s">
+      <c r="B291" s="163" t="s">
         <v>280</v>
       </c>
-      <c r="C291" s="157"/>
-      <c r="D291" s="157"/>
-      <c r="E291" s="157"/>
-      <c r="F291" s="157"/>
-      <c r="G291" s="157"/>
-      <c r="H291" s="157"/>
-      <c r="I291" s="157"/>
-      <c r="J291" s="157"/>
-      <c r="K291" s="157"/>
+      <c r="C291" s="152"/>
+      <c r="D291" s="152"/>
+      <c r="E291" s="152"/>
+      <c r="F291" s="152"/>
+      <c r="G291" s="152"/>
+      <c r="H291" s="152"/>
+      <c r="I291" s="152"/>
+      <c r="J291" s="152"/>
+      <c r="K291" s="152"/>
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B292" s="168"/>
-      <c r="C292" s="157"/>
-      <c r="D292" s="157"/>
-      <c r="E292" s="157"/>
-      <c r="F292" s="157"/>
-      <c r="G292" s="157"/>
-      <c r="H292" s="157"/>
-      <c r="I292" s="157"/>
-      <c r="J292" s="157"/>
-      <c r="K292" s="157"/>
+      <c r="B292" s="164"/>
+      <c r="C292" s="152"/>
+      <c r="D292" s="152"/>
+      <c r="E292" s="152"/>
+      <c r="F292" s="152"/>
+      <c r="G292" s="152"/>
+      <c r="H292" s="152"/>
+      <c r="I292" s="152"/>
+      <c r="J292" s="152"/>
+      <c r="K292" s="152"/>
     </row>
     <row r="293" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B293" s="168" t="s">
+      <c r="B293" s="164" t="s">
         <v>281</v>
       </c>
-      <c r="C293" s="157"/>
-      <c r="D293" s="157"/>
-      <c r="E293" s="157"/>
-      <c r="F293" s="157"/>
-      <c r="G293" s="157"/>
-      <c r="H293" s="157"/>
-      <c r="I293" s="157"/>
-      <c r="J293" s="157"/>
-      <c r="K293" s="157"/>
+      <c r="C293" s="152"/>
+      <c r="D293" s="152"/>
+      <c r="E293" s="152"/>
+      <c r="F293" s="152"/>
+      <c r="G293" s="152"/>
+      <c r="H293" s="152"/>
+      <c r="I293" s="152"/>
+      <c r="J293" s="152"/>
+      <c r="K293" s="152"/>
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B294" s="165" t="s">
+      <c r="B294" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="C294" s="157"/>
-      <c r="D294" s="157"/>
-      <c r="E294" s="157"/>
-      <c r="F294" s="157"/>
-      <c r="G294" s="157"/>
-      <c r="H294" s="157"/>
-      <c r="I294" s="157"/>
-      <c r="J294" s="157"/>
-      <c r="K294" s="157"/>
+      <c r="C294" s="152"/>
+      <c r="D294" s="152"/>
+      <c r="E294" s="152"/>
+      <c r="F294" s="152"/>
+      <c r="G294" s="152"/>
+      <c r="H294" s="152"/>
+      <c r="I294" s="152"/>
+      <c r="J294" s="152"/>
+      <c r="K294" s="152"/>
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B296" s="165" t="s">
+      <c r="B296" s="163" t="s">
         <v>283</v>
       </c>
-      <c r="C296" s="157"/>
-      <c r="D296" s="157"/>
-      <c r="E296" s="157"/>
-      <c r="F296" s="157"/>
-      <c r="G296" s="157"/>
-      <c r="H296" s="157"/>
-      <c r="I296" s="157"/>
-      <c r="J296" s="157"/>
-      <c r="K296" s="157"/>
+      <c r="C296" s="152"/>
+      <c r="D296" s="152"/>
+      <c r="E296" s="152"/>
+      <c r="F296" s="152"/>
+      <c r="G296" s="152"/>
+      <c r="H296" s="152"/>
+      <c r="I296" s="152"/>
+      <c r="J296" s="152"/>
+      <c r="K296" s="152"/>
     </row>
     <row r="303" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B303" s="167" t="s">
         <v>284</v>
       </c>
-      <c r="C303" s="152"/>
-      <c r="D303" s="152"/>
-      <c r="E303" s="152"/>
-      <c r="F303" s="152"/>
-      <c r="G303" s="152"/>
-      <c r="H303" s="152"/>
-      <c r="I303" s="152"/>
-      <c r="J303" s="152"/>
-      <c r="K303" s="153"/>
+      <c r="C303" s="156"/>
+      <c r="D303" s="156"/>
+      <c r="E303" s="156"/>
+      <c r="F303" s="156"/>
+      <c r="G303" s="156"/>
+      <c r="H303" s="156"/>
+      <c r="I303" s="156"/>
+      <c r="J303" s="156"/>
+      <c r="K303" s="154"/>
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B304" s="172" t="s">
+      <c r="B304" s="168" t="s">
         <v>285</v>
       </c>
-      <c r="C304" s="157"/>
-      <c r="D304" s="157"/>
-      <c r="E304" s="157"/>
-      <c r="F304" s="157"/>
-      <c r="G304" s="157"/>
-      <c r="H304" s="157"/>
-      <c r="I304" s="157"/>
-      <c r="J304" s="157"/>
-      <c r="K304" s="157"/>
+      <c r="C304" s="152"/>
+      <c r="D304" s="152"/>
+      <c r="E304" s="152"/>
+      <c r="F304" s="152"/>
+      <c r="G304" s="152"/>
+      <c r="H304" s="152"/>
+      <c r="I304" s="152"/>
+      <c r="J304" s="152"/>
+      <c r="K304" s="152"/>
     </row>
     <row r="306" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B306" s="167" t="s">
         <v>286</v>
       </c>
-      <c r="C306" s="152"/>
-      <c r="D306" s="152"/>
-      <c r="E306" s="152"/>
-      <c r="F306" s="152"/>
-      <c r="G306" s="152"/>
-      <c r="H306" s="152"/>
-      <c r="I306" s="152"/>
-      <c r="J306" s="153"/>
+      <c r="C306" s="156"/>
+      <c r="D306" s="156"/>
+      <c r="E306" s="156"/>
+      <c r="F306" s="156"/>
+      <c r="G306" s="156"/>
+      <c r="H306" s="156"/>
+      <c r="I306" s="156"/>
+      <c r="J306" s="154"/>
     </row>
     <row r="307" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B307" s="109" t="s">
@@ -8311,43 +8311,43 @@
       </c>
     </row>
     <row r="320" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B320" s="173" t="e">
+      <c r="B320" s="171" t="e">
         <f>CHOOSE(COUNTA(C308:C318), "«selected category»", "Multiple", "All")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C320" s="152"/>
-      <c r="D320" s="152"/>
-      <c r="E320" s="152"/>
-      <c r="F320" s="152"/>
-      <c r="G320" s="152"/>
-      <c r="H320" s="152"/>
-      <c r="I320" s="153"/>
+      <c r="C320" s="156"/>
+      <c r="D320" s="156"/>
+      <c r="E320" s="156"/>
+      <c r="F320" s="156"/>
+      <c r="G320" s="156"/>
+      <c r="H320" s="156"/>
+      <c r="I320" s="154"/>
     </row>
     <row r="322" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B322" s="167" t="s">
         <v>290</v>
       </c>
-      <c r="C322" s="152"/>
-      <c r="D322" s="152"/>
-      <c r="E322" s="152"/>
-      <c r="F322" s="152"/>
-      <c r="G322" s="152"/>
-      <c r="H322" s="152"/>
-      <c r="I322" s="152"/>
-      <c r="J322" s="153"/>
+      <c r="C322" s="156"/>
+      <c r="D322" s="156"/>
+      <c r="E322" s="156"/>
+      <c r="F322" s="156"/>
+      <c r="G322" s="156"/>
+      <c r="H322" s="156"/>
+      <c r="I322" s="156"/>
+      <c r="J322" s="154"/>
     </row>
     <row r="332" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B332" s="167" t="s">
         <v>291</v>
       </c>
-      <c r="C332" s="152"/>
-      <c r="D332" s="152"/>
-      <c r="E332" s="152"/>
-      <c r="F332" s="152"/>
-      <c r="G332" s="152"/>
-      <c r="H332" s="152"/>
-      <c r="I332" s="152"/>
-      <c r="J332" s="153"/>
+      <c r="C332" s="156"/>
+      <c r="D332" s="156"/>
+      <c r="E332" s="156"/>
+      <c r="F332" s="156"/>
+      <c r="G332" s="156"/>
+      <c r="H332" s="156"/>
+      <c r="I332" s="156"/>
+      <c r="J332" s="154"/>
     </row>
     <row r="333" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B333" s="109" t="s">
@@ -8493,14 +8493,14 @@
       <c r="B342" s="167" t="s">
         <v>301</v>
       </c>
-      <c r="C342" s="152"/>
-      <c r="D342" s="152"/>
-      <c r="E342" s="152"/>
-      <c r="F342" s="152"/>
-      <c r="G342" s="152"/>
-      <c r="H342" s="152"/>
-      <c r="I342" s="152"/>
-      <c r="J342" s="153"/>
+      <c r="C342" s="156"/>
+      <c r="D342" s="156"/>
+      <c r="E342" s="156"/>
+      <c r="F342" s="156"/>
+      <c r="G342" s="156"/>
+      <c r="H342" s="156"/>
+      <c r="I342" s="156"/>
+      <c r="J342" s="154"/>
     </row>
     <row r="343" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B343" s="109" t="s">
@@ -8574,29 +8574,29 @@
       <c r="B349" s="167" t="s">
         <v>305</v>
       </c>
-      <c r="C349" s="152"/>
-      <c r="D349" s="152"/>
-      <c r="E349" s="152"/>
-      <c r="F349" s="152"/>
-      <c r="G349" s="152"/>
-      <c r="H349" s="152"/>
-      <c r="I349" s="152"/>
-      <c r="J349" s="152"/>
-      <c r="K349" s="153"/>
+      <c r="C349" s="156"/>
+      <c r="D349" s="156"/>
+      <c r="E349" s="156"/>
+      <c r="F349" s="156"/>
+      <c r="G349" s="156"/>
+      <c r="H349" s="156"/>
+      <c r="I349" s="156"/>
+      <c r="J349" s="156"/>
+      <c r="K349" s="154"/>
     </row>
     <row r="350" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B350" s="172" t="s">
+      <c r="B350" s="168" t="s">
         <v>306</v>
       </c>
-      <c r="C350" s="157"/>
-      <c r="D350" s="157"/>
-      <c r="E350" s="157"/>
-      <c r="F350" s="157"/>
-      <c r="G350" s="157"/>
-      <c r="H350" s="157"/>
-      <c r="I350" s="157"/>
-      <c r="J350" s="157"/>
-      <c r="K350" s="157"/>
+      <c r="C350" s="152"/>
+      <c r="D350" s="152"/>
+      <c r="E350" s="152"/>
+      <c r="F350" s="152"/>
+      <c r="G350" s="152"/>
+      <c r="H350" s="152"/>
+      <c r="I350" s="152"/>
+      <c r="J350" s="152"/>
+      <c r="K350" s="152"/>
     </row>
     <row r="351" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B351" s="109" t="s">
@@ -8649,180 +8649,180 @@
       <c r="B358" s="167" t="s">
         <v>316</v>
       </c>
-      <c r="C358" s="152"/>
-      <c r="D358" s="152"/>
-      <c r="E358" s="152"/>
-      <c r="F358" s="152"/>
-      <c r="G358" s="152"/>
-      <c r="H358" s="152"/>
-      <c r="I358" s="152"/>
-      <c r="J358" s="152"/>
-      <c r="K358" s="153"/>
+      <c r="C358" s="156"/>
+      <c r="D358" s="156"/>
+      <c r="E358" s="156"/>
+      <c r="F358" s="156"/>
+      <c r="G358" s="156"/>
+      <c r="H358" s="156"/>
+      <c r="I358" s="156"/>
+      <c r="J358" s="156"/>
+      <c r="K358" s="154"/>
     </row>
     <row r="359" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B359" s="165" t="s">
+      <c r="B359" s="163" t="s">
         <v>317</v>
       </c>
-      <c r="C359" s="157"/>
-      <c r="D359" s="157"/>
-      <c r="E359" s="157"/>
-      <c r="F359" s="157"/>
-      <c r="G359" s="157"/>
-      <c r="H359" s="157"/>
-      <c r="I359" s="157"/>
-      <c r="J359" s="157"/>
-      <c r="K359" s="157"/>
+      <c r="C359" s="152"/>
+      <c r="D359" s="152"/>
+      <c r="E359" s="152"/>
+      <c r="F359" s="152"/>
+      <c r="G359" s="152"/>
+      <c r="H359" s="152"/>
+      <c r="I359" s="152"/>
+      <c r="J359" s="152"/>
+      <c r="K359" s="152"/>
     </row>
     <row r="361" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B361" s="165" t="s">
+      <c r="B361" s="163" t="s">
         <v>318</v>
       </c>
-      <c r="C361" s="157"/>
-      <c r="D361" s="157"/>
-      <c r="E361" s="157"/>
-      <c r="F361" s="157"/>
-      <c r="G361" s="157"/>
-      <c r="H361" s="157"/>
-      <c r="I361" s="157"/>
-      <c r="J361" s="157"/>
-      <c r="K361" s="157"/>
+      <c r="C361" s="152"/>
+      <c r="D361" s="152"/>
+      <c r="E361" s="152"/>
+      <c r="F361" s="152"/>
+      <c r="G361" s="152"/>
+      <c r="H361" s="152"/>
+      <c r="I361" s="152"/>
+      <c r="J361" s="152"/>
+      <c r="K361" s="152"/>
     </row>
     <row r="362" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B362" s="165" t="s">
+      <c r="B362" s="163" t="s">
         <v>319</v>
       </c>
-      <c r="C362" s="157"/>
-      <c r="D362" s="157"/>
-      <c r="E362" s="157"/>
-      <c r="F362" s="157"/>
-      <c r="G362" s="157"/>
-      <c r="H362" s="157"/>
-      <c r="I362" s="157"/>
-      <c r="J362" s="157"/>
-      <c r="K362" s="157"/>
+      <c r="C362" s="152"/>
+      <c r="D362" s="152"/>
+      <c r="E362" s="152"/>
+      <c r="F362" s="152"/>
+      <c r="G362" s="152"/>
+      <c r="H362" s="152"/>
+      <c r="I362" s="152"/>
+      <c r="J362" s="152"/>
+      <c r="K362" s="152"/>
     </row>
     <row r="364" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B364" s="165"/>
-      <c r="C364" s="157"/>
-      <c r="D364" s="157"/>
-      <c r="E364" s="157"/>
-      <c r="F364" s="157"/>
-      <c r="G364" s="157"/>
-      <c r="H364" s="157"/>
-      <c r="I364" s="157"/>
-      <c r="J364" s="157"/>
-      <c r="K364" s="157"/>
+      <c r="B364" s="163"/>
+      <c r="C364" s="152"/>
+      <c r="D364" s="152"/>
+      <c r="E364" s="152"/>
+      <c r="F364" s="152"/>
+      <c r="G364" s="152"/>
+      <c r="H364" s="152"/>
+      <c r="I364" s="152"/>
+      <c r="J364" s="152"/>
+      <c r="K364" s="152"/>
     </row>
     <row r="365" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B365" s="168" t="s">
+      <c r="B365" s="164" t="s">
         <v>320</v>
       </c>
-      <c r="C365" s="157"/>
-      <c r="D365" s="157"/>
-      <c r="E365" s="157"/>
-      <c r="F365" s="157"/>
-      <c r="G365" s="157"/>
-      <c r="H365" s="157"/>
-      <c r="I365" s="157"/>
-      <c r="J365" s="157"/>
-      <c r="K365" s="157"/>
+      <c r="C365" s="152"/>
+      <c r="D365" s="152"/>
+      <c r="E365" s="152"/>
+      <c r="F365" s="152"/>
+      <c r="G365" s="152"/>
+      <c r="H365" s="152"/>
+      <c r="I365" s="152"/>
+      <c r="J365" s="152"/>
+      <c r="K365" s="152"/>
     </row>
     <row r="366" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B366" s="168" t="s">
+      <c r="B366" s="164" t="s">
         <v>321</v>
       </c>
-      <c r="C366" s="157"/>
-      <c r="D366" s="157"/>
-      <c r="E366" s="157"/>
-      <c r="F366" s="157"/>
-      <c r="G366" s="157"/>
-      <c r="H366" s="157"/>
-      <c r="I366" s="157"/>
-      <c r="J366" s="157"/>
-      <c r="K366" s="157"/>
+      <c r="C366" s="152"/>
+      <c r="D366" s="152"/>
+      <c r="E366" s="152"/>
+      <c r="F366" s="152"/>
+      <c r="G366" s="152"/>
+      <c r="H366" s="152"/>
+      <c r="I366" s="152"/>
+      <c r="J366" s="152"/>
+      <c r="K366" s="152"/>
     </row>
     <row r="367" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B367" s="168" t="s">
+      <c r="B367" s="164" t="s">
         <v>322</v>
       </c>
-      <c r="C367" s="157"/>
-      <c r="D367" s="157"/>
-      <c r="E367" s="157"/>
-      <c r="F367" s="157"/>
-      <c r="G367" s="157"/>
-      <c r="H367" s="157"/>
-      <c r="I367" s="157"/>
-      <c r="J367" s="157"/>
-      <c r="K367" s="157"/>
+      <c r="C367" s="152"/>
+      <c r="D367" s="152"/>
+      <c r="E367" s="152"/>
+      <c r="F367" s="152"/>
+      <c r="G367" s="152"/>
+      <c r="H367" s="152"/>
+      <c r="I367" s="152"/>
+      <c r="J367" s="152"/>
+      <c r="K367" s="152"/>
     </row>
     <row r="368" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B368" s="168" t="s">
+      <c r="B368" s="164" t="s">
         <v>323</v>
       </c>
-      <c r="C368" s="157"/>
-      <c r="D368" s="157"/>
-      <c r="E368" s="157"/>
-      <c r="F368" s="157"/>
-      <c r="G368" s="157"/>
-      <c r="H368" s="157"/>
-      <c r="I368" s="157"/>
-      <c r="J368" s="157"/>
-      <c r="K368" s="157"/>
+      <c r="C368" s="152"/>
+      <c r="D368" s="152"/>
+      <c r="E368" s="152"/>
+      <c r="F368" s="152"/>
+      <c r="G368" s="152"/>
+      <c r="H368" s="152"/>
+      <c r="I368" s="152"/>
+      <c r="J368" s="152"/>
+      <c r="K368" s="152"/>
     </row>
     <row r="369" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B369" s="168" t="s">
+      <c r="B369" s="164" t="s">
         <v>324</v>
       </c>
-      <c r="C369" s="157"/>
-      <c r="D369" s="157"/>
-      <c r="E369" s="157"/>
-      <c r="F369" s="157"/>
-      <c r="G369" s="157"/>
-      <c r="H369" s="157"/>
-      <c r="I369" s="157"/>
-      <c r="J369" s="157"/>
-      <c r="K369" s="157"/>
+      <c r="C369" s="152"/>
+      <c r="D369" s="152"/>
+      <c r="E369" s="152"/>
+      <c r="F369" s="152"/>
+      <c r="G369" s="152"/>
+      <c r="H369" s="152"/>
+      <c r="I369" s="152"/>
+      <c r="J369" s="152"/>
+      <c r="K369" s="152"/>
     </row>
     <row r="372" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B372" s="167" t="s">
         <v>325</v>
       </c>
-      <c r="C372" s="152"/>
-      <c r="D372" s="152"/>
-      <c r="E372" s="152"/>
-      <c r="F372" s="152"/>
-      <c r="G372" s="152"/>
-      <c r="H372" s="152"/>
-      <c r="I372" s="152"/>
-      <c r="J372" s="152"/>
-      <c r="K372" s="153"/>
+      <c r="C372" s="156"/>
+      <c r="D372" s="156"/>
+      <c r="E372" s="156"/>
+      <c r="F372" s="156"/>
+      <c r="G372" s="156"/>
+      <c r="H372" s="156"/>
+      <c r="I372" s="156"/>
+      <c r="J372" s="156"/>
+      <c r="K372" s="154"/>
     </row>
     <row r="373" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B373" s="163" t="s">
+      <c r="B373" s="169" t="s">
         <v>326</v>
       </c>
-      <c r="C373" s="157"/>
-      <c r="D373" s="157"/>
-      <c r="E373" s="157"/>
-      <c r="F373" s="157"/>
-      <c r="G373" s="157"/>
-      <c r="H373" s="157"/>
-      <c r="I373" s="157"/>
-      <c r="J373" s="157"/>
-      <c r="K373" s="157"/>
+      <c r="C373" s="152"/>
+      <c r="D373" s="152"/>
+      <c r="E373" s="152"/>
+      <c r="F373" s="152"/>
+      <c r="G373" s="152"/>
+      <c r="H373" s="152"/>
+      <c r="I373" s="152"/>
+      <c r="J373" s="152"/>
+      <c r="K373" s="152"/>
     </row>
     <row r="375" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B375" s="167" t="s">
         <v>327</v>
       </c>
-      <c r="C375" s="152"/>
-      <c r="D375" s="152"/>
-      <c r="E375" s="152"/>
-      <c r="F375" s="152"/>
-      <c r="G375" s="152"/>
-      <c r="H375" s="152"/>
-      <c r="I375" s="152"/>
-      <c r="J375" s="153"/>
+      <c r="C375" s="156"/>
+      <c r="D375" s="156"/>
+      <c r="E375" s="156"/>
+      <c r="F375" s="156"/>
+      <c r="G375" s="156"/>
+      <c r="H375" s="156"/>
+      <c r="I375" s="156"/>
+      <c r="J375" s="154"/>
     </row>
     <row r="376" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B376" s="109" t="s">
@@ -9311,27 +9311,27 @@
       <c r="B399" s="167" t="s">
         <v>351</v>
       </c>
-      <c r="C399" s="152"/>
-      <c r="D399" s="152"/>
-      <c r="E399" s="152"/>
-      <c r="F399" s="152"/>
-      <c r="G399" s="152"/>
-      <c r="H399" s="152"/>
-      <c r="I399" s="152"/>
-      <c r="J399" s="153"/>
+      <c r="C399" s="156"/>
+      <c r="D399" s="156"/>
+      <c r="E399" s="156"/>
+      <c r="F399" s="156"/>
+      <c r="G399" s="156"/>
+      <c r="H399" s="156"/>
+      <c r="I399" s="156"/>
+      <c r="J399" s="154"/>
     </row>
     <row r="418" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B418" s="167" t="s">
         <v>352</v>
       </c>
-      <c r="C418" s="152"/>
-      <c r="D418" s="152"/>
-      <c r="E418" s="152"/>
-      <c r="F418" s="152"/>
-      <c r="G418" s="152"/>
-      <c r="H418" s="152"/>
-      <c r="I418" s="152"/>
-      <c r="J418" s="153"/>
+      <c r="C418" s="156"/>
+      <c r="D418" s="156"/>
+      <c r="E418" s="156"/>
+      <c r="F418" s="156"/>
+      <c r="G418" s="156"/>
+      <c r="H418" s="156"/>
+      <c r="I418" s="156"/>
+      <c r="J418" s="154"/>
     </row>
     <row r="419" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B419" s="109" t="s">
@@ -9753,14 +9753,14 @@
       <c r="B437" s="167" t="s">
         <v>355</v>
       </c>
-      <c r="C437" s="152"/>
-      <c r="D437" s="152"/>
-      <c r="E437" s="152"/>
-      <c r="F437" s="152"/>
-      <c r="G437" s="152"/>
-      <c r="H437" s="152"/>
-      <c r="I437" s="152"/>
-      <c r="J437" s="153"/>
+      <c r="C437" s="156"/>
+      <c r="D437" s="156"/>
+      <c r="E437" s="156"/>
+      <c r="F437" s="156"/>
+      <c r="G437" s="156"/>
+      <c r="H437" s="156"/>
+      <c r="I437" s="156"/>
+      <c r="J437" s="154"/>
     </row>
     <row r="438" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B438" s="109" t="s">
@@ -9868,14 +9868,14 @@
       <c r="B456" s="167" t="s">
         <v>367</v>
       </c>
-      <c r="C456" s="152"/>
-      <c r="D456" s="152"/>
-      <c r="E456" s="152"/>
-      <c r="F456" s="152"/>
-      <c r="G456" s="152"/>
-      <c r="H456" s="152"/>
-      <c r="I456" s="152"/>
-      <c r="J456" s="153"/>
+      <c r="C456" s="156"/>
+      <c r="D456" s="156"/>
+      <c r="E456" s="156"/>
+      <c r="F456" s="156"/>
+      <c r="G456" s="156"/>
+      <c r="H456" s="156"/>
+      <c r="I456" s="156"/>
+      <c r="J456" s="154"/>
     </row>
     <row r="457" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B457" s="109" t="s">
@@ -10249,112 +10249,112 @@
       <c r="B475" s="167" t="s">
         <v>412</v>
       </c>
-      <c r="C475" s="152"/>
-      <c r="D475" s="152"/>
-      <c r="E475" s="152"/>
-      <c r="F475" s="152"/>
-      <c r="G475" s="152"/>
-      <c r="H475" s="152"/>
-      <c r="I475" s="152"/>
-      <c r="J475" s="152"/>
-      <c r="K475" s="153"/>
+      <c r="C475" s="156"/>
+      <c r="D475" s="156"/>
+      <c r="E475" s="156"/>
+      <c r="F475" s="156"/>
+      <c r="G475" s="156"/>
+      <c r="H475" s="156"/>
+      <c r="I475" s="156"/>
+      <c r="J475" s="156"/>
+      <c r="K475" s="154"/>
     </row>
     <row r="476" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B476" s="165" t="s">
+      <c r="B476" s="163" t="s">
         <v>413</v>
       </c>
-      <c r="C476" s="157"/>
-      <c r="D476" s="157"/>
-      <c r="E476" s="157"/>
-      <c r="F476" s="157"/>
-      <c r="G476" s="157"/>
-      <c r="H476" s="157"/>
-      <c r="I476" s="157"/>
-      <c r="J476" s="157"/>
-      <c r="K476" s="157"/>
+      <c r="C476" s="152"/>
+      <c r="D476" s="152"/>
+      <c r="E476" s="152"/>
+      <c r="F476" s="152"/>
+      <c r="G476" s="152"/>
+      <c r="H476" s="152"/>
+      <c r="I476" s="152"/>
+      <c r="J476" s="152"/>
+      <c r="K476" s="152"/>
     </row>
     <row r="478" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B478" s="165" t="s">
+      <c r="B478" s="163" t="s">
         <v>414</v>
       </c>
-      <c r="C478" s="157"/>
-      <c r="D478" s="157"/>
-      <c r="E478" s="157"/>
-      <c r="F478" s="157"/>
-      <c r="G478" s="157"/>
-      <c r="H478" s="157"/>
-      <c r="I478" s="157"/>
-      <c r="J478" s="157"/>
-      <c r="K478" s="157"/>
+      <c r="C478" s="152"/>
+      <c r="D478" s="152"/>
+      <c r="E478" s="152"/>
+      <c r="F478" s="152"/>
+      <c r="G478" s="152"/>
+      <c r="H478" s="152"/>
+      <c r="I478" s="152"/>
+      <c r="J478" s="152"/>
+      <c r="K478" s="152"/>
     </row>
     <row r="479" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B479" s="165" t="s">
+      <c r="B479" s="163" t="s">
         <v>415</v>
       </c>
-      <c r="C479" s="157"/>
-      <c r="D479" s="157"/>
-      <c r="E479" s="157"/>
-      <c r="F479" s="157"/>
-      <c r="G479" s="157"/>
-      <c r="H479" s="157"/>
-      <c r="I479" s="157"/>
-      <c r="J479" s="157"/>
-      <c r="K479" s="157"/>
+      <c r="C479" s="152"/>
+      <c r="D479" s="152"/>
+      <c r="E479" s="152"/>
+      <c r="F479" s="152"/>
+      <c r="G479" s="152"/>
+      <c r="H479" s="152"/>
+      <c r="I479" s="152"/>
+      <c r="J479" s="152"/>
+      <c r="K479" s="152"/>
     </row>
     <row r="480" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B480" s="165" t="s">
+      <c r="B480" s="163" t="s">
         <v>416</v>
       </c>
-      <c r="C480" s="157"/>
-      <c r="D480" s="157"/>
-      <c r="E480" s="157"/>
-      <c r="F480" s="157"/>
-      <c r="G480" s="157"/>
-      <c r="H480" s="157"/>
-      <c r="I480" s="157"/>
-      <c r="J480" s="157"/>
-      <c r="K480" s="157"/>
+      <c r="C480" s="152"/>
+      <c r="D480" s="152"/>
+      <c r="E480" s="152"/>
+      <c r="F480" s="152"/>
+      <c r="G480" s="152"/>
+      <c r="H480" s="152"/>
+      <c r="I480" s="152"/>
+      <c r="J480" s="152"/>
+      <c r="K480" s="152"/>
     </row>
     <row r="483" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B483" s="167" t="s">
         <v>417</v>
       </c>
-      <c r="C483" s="152"/>
-      <c r="D483" s="152"/>
-      <c r="E483" s="152"/>
-      <c r="F483" s="152"/>
-      <c r="G483" s="152"/>
-      <c r="H483" s="152"/>
-      <c r="I483" s="152"/>
-      <c r="J483" s="152"/>
-      <c r="K483" s="153"/>
+      <c r="C483" s="156"/>
+      <c r="D483" s="156"/>
+      <c r="E483" s="156"/>
+      <c r="F483" s="156"/>
+      <c r="G483" s="156"/>
+      <c r="H483" s="156"/>
+      <c r="I483" s="156"/>
+      <c r="J483" s="156"/>
+      <c r="K483" s="154"/>
     </row>
     <row r="484" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B484" s="172" t="s">
+      <c r="B484" s="168" t="s">
         <v>418</v>
       </c>
-      <c r="C484" s="157"/>
-      <c r="D484" s="157"/>
-      <c r="E484" s="157"/>
-      <c r="F484" s="157"/>
-      <c r="G484" s="157"/>
-      <c r="H484" s="157"/>
-      <c r="I484" s="157"/>
-      <c r="J484" s="157"/>
-      <c r="K484" s="157"/>
+      <c r="C484" s="152"/>
+      <c r="D484" s="152"/>
+      <c r="E484" s="152"/>
+      <c r="F484" s="152"/>
+      <c r="G484" s="152"/>
+      <c r="H484" s="152"/>
+      <c r="I484" s="152"/>
+      <c r="J484" s="152"/>
+      <c r="K484" s="152"/>
     </row>
     <row r="486" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B486" s="167" t="s">
         <v>419</v>
       </c>
-      <c r="C486" s="152"/>
-      <c r="D486" s="152"/>
-      <c r="E486" s="152"/>
-      <c r="F486" s="152"/>
-      <c r="G486" s="152"/>
-      <c r="H486" s="152"/>
-      <c r="I486" s="152"/>
-      <c r="J486" s="153"/>
+      <c r="C486" s="156"/>
+      <c r="D486" s="156"/>
+      <c r="E486" s="156"/>
+      <c r="F486" s="156"/>
+      <c r="G486" s="156"/>
+      <c r="H486" s="156"/>
+      <c r="I486" s="156"/>
+      <c r="J486" s="154"/>
     </row>
     <row r="487" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B487" s="109" t="s">
@@ -10437,14 +10437,14 @@
       <c r="B497" s="167" t="s">
         <v>430</v>
       </c>
-      <c r="C497" s="152"/>
-      <c r="D497" s="152"/>
-      <c r="E497" s="152"/>
-      <c r="F497" s="152"/>
-      <c r="G497" s="152"/>
-      <c r="H497" s="152"/>
-      <c r="I497" s="152"/>
-      <c r="J497" s="153"/>
+      <c r="C497" s="156"/>
+      <c r="D497" s="156"/>
+      <c r="E497" s="156"/>
+      <c r="F497" s="156"/>
+      <c r="G497" s="156"/>
+      <c r="H497" s="156"/>
+      <c r="I497" s="156"/>
+      <c r="J497" s="154"/>
     </row>
     <row r="498" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B498" s="109" t="s">
@@ -10550,55 +10550,55 @@
       <c r="B508" s="167" t="s">
         <v>444</v>
       </c>
-      <c r="C508" s="152"/>
-      <c r="D508" s="152"/>
-      <c r="E508" s="152"/>
-      <c r="F508" s="152"/>
-      <c r="G508" s="152"/>
-      <c r="H508" s="152"/>
-      <c r="I508" s="152"/>
-      <c r="J508" s="152"/>
-      <c r="K508" s="153"/>
+      <c r="C508" s="156"/>
+      <c r="D508" s="156"/>
+      <c r="E508" s="156"/>
+      <c r="F508" s="156"/>
+      <c r="G508" s="156"/>
+      <c r="H508" s="156"/>
+      <c r="I508" s="156"/>
+      <c r="J508" s="156"/>
+      <c r="K508" s="154"/>
     </row>
     <row r="509" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B509" s="172" t="s">
+      <c r="B509" s="168" t="s">
         <v>445</v>
       </c>
-      <c r="C509" s="157"/>
-      <c r="D509" s="157"/>
-      <c r="E509" s="157"/>
-      <c r="F509" s="157"/>
-      <c r="G509" s="157"/>
-      <c r="H509" s="157"/>
-      <c r="I509" s="157"/>
-      <c r="J509" s="157"/>
-      <c r="K509" s="157"/>
+      <c r="C509" s="152"/>
+      <c r="D509" s="152"/>
+      <c r="E509" s="152"/>
+      <c r="F509" s="152"/>
+      <c r="G509" s="152"/>
+      <c r="H509" s="152"/>
+      <c r="I509" s="152"/>
+      <c r="J509" s="152"/>
+      <c r="K509" s="152"/>
     </row>
     <row r="511" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B511" s="167" t="s">
         <v>446</v>
       </c>
-      <c r="C511" s="152"/>
-      <c r="D511" s="152"/>
-      <c r="E511" s="152"/>
-      <c r="F511" s="152"/>
-      <c r="G511" s="152"/>
-      <c r="H511" s="152"/>
-      <c r="I511" s="152"/>
-      <c r="J511" s="153"/>
+      <c r="C511" s="156"/>
+      <c r="D511" s="156"/>
+      <c r="E511" s="156"/>
+      <c r="F511" s="156"/>
+      <c r="G511" s="156"/>
+      <c r="H511" s="156"/>
+      <c r="I511" s="156"/>
+      <c r="J511" s="154"/>
     </row>
     <row r="521" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B521" s="167" t="s">
         <v>447</v>
       </c>
-      <c r="C521" s="152"/>
-      <c r="D521" s="152"/>
-      <c r="E521" s="152"/>
-      <c r="F521" s="152"/>
-      <c r="G521" s="152"/>
-      <c r="H521" s="152"/>
-      <c r="I521" s="152"/>
-      <c r="J521" s="153"/>
+      <c r="C521" s="156"/>
+      <c r="D521" s="156"/>
+      <c r="E521" s="156"/>
+      <c r="F521" s="156"/>
+      <c r="G521" s="156"/>
+      <c r="H521" s="156"/>
+      <c r="I521" s="156"/>
+      <c r="J521" s="154"/>
     </row>
     <row r="522" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B522" s="109" t="s">
@@ -10916,55 +10916,55 @@
       <c r="B536" s="167" t="s">
         <v>451</v>
       </c>
-      <c r="C536" s="152"/>
-      <c r="D536" s="152"/>
-      <c r="E536" s="152"/>
-      <c r="F536" s="152"/>
-      <c r="G536" s="152"/>
-      <c r="H536" s="152"/>
-      <c r="I536" s="152"/>
-      <c r="J536" s="152"/>
-      <c r="K536" s="153"/>
+      <c r="C536" s="156"/>
+      <c r="D536" s="156"/>
+      <c r="E536" s="156"/>
+      <c r="F536" s="156"/>
+      <c r="G536" s="156"/>
+      <c r="H536" s="156"/>
+      <c r="I536" s="156"/>
+      <c r="J536" s="156"/>
+      <c r="K536" s="154"/>
     </row>
     <row r="537" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B537" s="172" t="s">
+      <c r="B537" s="168" t="s">
         <v>452</v>
       </c>
-      <c r="C537" s="157"/>
-      <c r="D537" s="157"/>
-      <c r="E537" s="157"/>
-      <c r="F537" s="157"/>
-      <c r="G537" s="157"/>
-      <c r="H537" s="157"/>
-      <c r="I537" s="157"/>
-      <c r="J537" s="157"/>
-      <c r="K537" s="157"/>
+      <c r="C537" s="152"/>
+      <c r="D537" s="152"/>
+      <c r="E537" s="152"/>
+      <c r="F537" s="152"/>
+      <c r="G537" s="152"/>
+      <c r="H537" s="152"/>
+      <c r="I537" s="152"/>
+      <c r="J537" s="152"/>
+      <c r="K537" s="152"/>
     </row>
     <row r="539" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B539" s="167" t="s">
         <v>453</v>
       </c>
-      <c r="C539" s="152"/>
-      <c r="D539" s="152"/>
-      <c r="E539" s="152"/>
-      <c r="F539" s="152"/>
-      <c r="G539" s="152"/>
-      <c r="H539" s="152"/>
-      <c r="I539" s="152"/>
-      <c r="J539" s="153"/>
+      <c r="C539" s="156"/>
+      <c r="D539" s="156"/>
+      <c r="E539" s="156"/>
+      <c r="F539" s="156"/>
+      <c r="G539" s="156"/>
+      <c r="H539" s="156"/>
+      <c r="I539" s="156"/>
+      <c r="J539" s="154"/>
     </row>
     <row r="549" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B549" s="167" t="s">
         <v>454</v>
       </c>
-      <c r="C549" s="152"/>
-      <c r="D549" s="152"/>
-      <c r="E549" s="152"/>
-      <c r="F549" s="152"/>
-      <c r="G549" s="152"/>
-      <c r="H549" s="152"/>
-      <c r="I549" s="152"/>
-      <c r="J549" s="153"/>
+      <c r="C549" s="156"/>
+      <c r="D549" s="156"/>
+      <c r="E549" s="156"/>
+      <c r="F549" s="156"/>
+      <c r="G549" s="156"/>
+      <c r="H549" s="156"/>
+      <c r="I549" s="156"/>
+      <c r="J549" s="154"/>
     </row>
     <row r="550" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B550" s="109" t="s">
@@ -11185,42 +11185,42 @@
       <c r="B564" s="167" t="s">
         <v>460</v>
       </c>
-      <c r="C564" s="152"/>
-      <c r="D564" s="152"/>
-      <c r="E564" s="152"/>
-      <c r="F564" s="152"/>
-      <c r="G564" s="152"/>
-      <c r="H564" s="152"/>
-      <c r="I564" s="152"/>
-      <c r="J564" s="152"/>
-      <c r="K564" s="153"/>
+      <c r="C564" s="156"/>
+      <c r="D564" s="156"/>
+      <c r="E564" s="156"/>
+      <c r="F564" s="156"/>
+      <c r="G564" s="156"/>
+      <c r="H564" s="156"/>
+      <c r="I564" s="156"/>
+      <c r="J564" s="156"/>
+      <c r="K564" s="154"/>
     </row>
     <row r="565" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B565" s="172" t="s">
+      <c r="B565" s="168" t="s">
         <v>461</v>
       </c>
-      <c r="C565" s="157"/>
-      <c r="D565" s="157"/>
-      <c r="E565" s="157"/>
-      <c r="F565" s="157"/>
-      <c r="G565" s="157"/>
-      <c r="H565" s="157"/>
-      <c r="I565" s="157"/>
-      <c r="J565" s="157"/>
-      <c r="K565" s="157"/>
+      <c r="C565" s="152"/>
+      <c r="D565" s="152"/>
+      <c r="E565" s="152"/>
+      <c r="F565" s="152"/>
+      <c r="G565" s="152"/>
+      <c r="H565" s="152"/>
+      <c r="I565" s="152"/>
+      <c r="J565" s="152"/>
+      <c r="K565" s="152"/>
     </row>
     <row r="567" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B567" s="167" t="s">
         <v>462</v>
       </c>
-      <c r="C567" s="152"/>
-      <c r="D567" s="152"/>
-      <c r="E567" s="152"/>
-      <c r="F567" s="152"/>
-      <c r="G567" s="152"/>
-      <c r="H567" s="152"/>
-      <c r="I567" s="152"/>
-      <c r="J567" s="153"/>
+      <c r="C567" s="156"/>
+      <c r="D567" s="156"/>
+      <c r="E567" s="156"/>
+      <c r="F567" s="156"/>
+      <c r="G567" s="156"/>
+      <c r="H567" s="156"/>
+      <c r="I567" s="156"/>
+      <c r="J567" s="154"/>
     </row>
     <row r="568" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B568" s="109" t="s">
@@ -11690,14 +11690,14 @@
       <c r="B585" s="167" t="s">
         <v>470</v>
       </c>
-      <c r="C585" s="152"/>
-      <c r="D585" s="152"/>
-      <c r="E585" s="152"/>
-      <c r="F585" s="152"/>
-      <c r="G585" s="152"/>
-      <c r="H585" s="152"/>
-      <c r="I585" s="152"/>
-      <c r="J585" s="153"/>
+      <c r="C585" s="156"/>
+      <c r="D585" s="156"/>
+      <c r="E585" s="156"/>
+      <c r="F585" s="156"/>
+      <c r="G585" s="156"/>
+      <c r="H585" s="156"/>
+      <c r="I585" s="156"/>
+      <c r="J585" s="154"/>
     </row>
     <row r="586" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B586" s="109" t="s">
@@ -11819,42 +11819,42 @@
       <c r="B592" s="167" t="s">
         <v>474</v>
       </c>
-      <c r="C592" s="152"/>
-      <c r="D592" s="152"/>
-      <c r="E592" s="152"/>
-      <c r="F592" s="152"/>
-      <c r="G592" s="152"/>
-      <c r="H592" s="152"/>
-      <c r="I592" s="152"/>
-      <c r="J592" s="152"/>
-      <c r="K592" s="153"/>
+      <c r="C592" s="156"/>
+      <c r="D592" s="156"/>
+      <c r="E592" s="156"/>
+      <c r="F592" s="156"/>
+      <c r="G592" s="156"/>
+      <c r="H592" s="156"/>
+      <c r="I592" s="156"/>
+      <c r="J592" s="156"/>
+      <c r="K592" s="154"/>
     </row>
     <row r="593" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B593" s="172" t="s">
+      <c r="B593" s="168" t="s">
         <v>475</v>
       </c>
-      <c r="C593" s="157"/>
-      <c r="D593" s="157"/>
-      <c r="E593" s="157"/>
-      <c r="F593" s="157"/>
-      <c r="G593" s="157"/>
-      <c r="H593" s="157"/>
-      <c r="I593" s="157"/>
-      <c r="J593" s="157"/>
-      <c r="K593" s="157"/>
+      <c r="C593" s="152"/>
+      <c r="D593" s="152"/>
+      <c r="E593" s="152"/>
+      <c r="F593" s="152"/>
+      <c r="G593" s="152"/>
+      <c r="H593" s="152"/>
+      <c r="I593" s="152"/>
+      <c r="J593" s="152"/>
+      <c r="K593" s="152"/>
     </row>
     <row r="595" spans="2:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B595" s="167" t="s">
         <v>476</v>
       </c>
-      <c r="C595" s="152"/>
-      <c r="D595" s="152"/>
-      <c r="E595" s="152"/>
-      <c r="F595" s="152"/>
-      <c r="G595" s="152"/>
-      <c r="H595" s="152"/>
-      <c r="I595" s="152"/>
-      <c r="J595" s="153"/>
+      <c r="C595" s="156"/>
+      <c r="D595" s="156"/>
+      <c r="E595" s="156"/>
+      <c r="F595" s="156"/>
+      <c r="G595" s="156"/>
+      <c r="H595" s="156"/>
+      <c r="I595" s="156"/>
+      <c r="J595" s="154"/>
     </row>
     <row r="596" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B596" s="109" t="s">
@@ -11979,14 +11979,14 @@
       <c r="B614" s="167" t="s">
         <v>503</v>
       </c>
-      <c r="C614" s="152"/>
-      <c r="D614" s="152"/>
-      <c r="E614" s="152"/>
-      <c r="F614" s="152"/>
-      <c r="G614" s="152"/>
-      <c r="H614" s="152"/>
-      <c r="I614" s="152"/>
-      <c r="J614" s="153"/>
+      <c r="C614" s="156"/>
+      <c r="D614" s="156"/>
+      <c r="E614" s="156"/>
+      <c r="F614" s="156"/>
+      <c r="G614" s="156"/>
+      <c r="H614" s="156"/>
+      <c r="I614" s="156"/>
+      <c r="J614" s="154"/>
     </row>
     <row r="615" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B615" s="109" t="s">
@@ -12043,14 +12043,14 @@
       <c r="B623" s="167" t="s">
         <v>517</v>
       </c>
-      <c r="C623" s="152"/>
-      <c r="D623" s="152"/>
-      <c r="E623" s="152"/>
-      <c r="F623" s="152"/>
-      <c r="G623" s="152"/>
-      <c r="H623" s="152"/>
-      <c r="I623" s="152"/>
-      <c r="J623" s="153"/>
+      <c r="C623" s="156"/>
+      <c r="D623" s="156"/>
+      <c r="E623" s="156"/>
+      <c r="F623" s="156"/>
+      <c r="G623" s="156"/>
+      <c r="H623" s="156"/>
+      <c r="I623" s="156"/>
+      <c r="J623" s="154"/>
     </row>
     <row r="624" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B624" s="109" t="s">
@@ -12153,15 +12153,81 @@
     </row>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="B480:K480"/>
-    <mergeCell ref="B250:K250"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B149:J149"/>
-    <mergeCell ref="B215:J215"/>
-    <mergeCell ref="B289:K289"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B539:J539"/>
-    <mergeCell ref="B322:J322"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B241:K241"/>
+    <mergeCell ref="B256:K256"/>
+    <mergeCell ref="B369:K369"/>
+    <mergeCell ref="B191:J191"/>
+    <mergeCell ref="B205:J205"/>
+    <mergeCell ref="B368:K368"/>
+    <mergeCell ref="B211:J211"/>
+    <mergeCell ref="B358:K358"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B593:K593"/>
+    <mergeCell ref="B304:K304"/>
+    <mergeCell ref="B372:K372"/>
+    <mergeCell ref="B157:J157"/>
+    <mergeCell ref="B320:I320"/>
+    <mergeCell ref="B359:K359"/>
+    <mergeCell ref="B251:K251"/>
+    <mergeCell ref="B296:K296"/>
+    <mergeCell ref="B361:K361"/>
+    <mergeCell ref="B218:K218"/>
+    <mergeCell ref="B158:J158"/>
+    <mergeCell ref="B486:J486"/>
+    <mergeCell ref="B121:J121"/>
+    <mergeCell ref="B148:J148"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="B189:J189"/>
+    <mergeCell ref="B585:J585"/>
+    <mergeCell ref="B188:J188"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B362:K362"/>
+    <mergeCell ref="B150:J150"/>
+    <mergeCell ref="B190:J190"/>
+    <mergeCell ref="B456:J456"/>
+    <mergeCell ref="B567:J567"/>
+    <mergeCell ref="B478:K478"/>
+    <mergeCell ref="B536:K536"/>
+    <mergeCell ref="B437:J437"/>
+    <mergeCell ref="B342:J342"/>
+    <mergeCell ref="B277:K277"/>
+    <mergeCell ref="B479:K479"/>
+    <mergeCell ref="B375:J375"/>
+    <mergeCell ref="B595:J595"/>
+    <mergeCell ref="B521:J521"/>
+    <mergeCell ref="B483:K483"/>
+    <mergeCell ref="B291:K291"/>
+    <mergeCell ref="B475:K475"/>
+    <mergeCell ref="B511:J511"/>
+    <mergeCell ref="B293:K293"/>
+    <mergeCell ref="B290:K290"/>
+    <mergeCell ref="B367:K367"/>
+    <mergeCell ref="B288:K288"/>
+    <mergeCell ref="B332:J332"/>
+    <mergeCell ref="B287:K287"/>
+    <mergeCell ref="B549:J549"/>
+    <mergeCell ref="B306:J306"/>
+    <mergeCell ref="B508:K508"/>
+    <mergeCell ref="B229:K229"/>
+    <mergeCell ref="B194:J194"/>
+    <mergeCell ref="B349:K349"/>
+    <mergeCell ref="B214:J214"/>
+    <mergeCell ref="B476:K476"/>
+    <mergeCell ref="B210:J210"/>
+    <mergeCell ref="B364:K364"/>
+    <mergeCell ref="B373:K373"/>
+    <mergeCell ref="B219:K219"/>
+    <mergeCell ref="B212:J212"/>
+    <mergeCell ref="B259:K259"/>
+    <mergeCell ref="B206:J206"/>
+    <mergeCell ref="B209:J209"/>
+    <mergeCell ref="B267:K267"/>
+    <mergeCell ref="B202:J202"/>
+    <mergeCell ref="B253:K253"/>
+    <mergeCell ref="B230:K230"/>
+    <mergeCell ref="B257:K257"/>
+    <mergeCell ref="B254:K254"/>
     <mergeCell ref="B565:K565"/>
     <mergeCell ref="B623:J623"/>
     <mergeCell ref="B266:K266"/>
@@ -12186,89 +12252,23 @@
     <mergeCell ref="B484:K484"/>
     <mergeCell ref="B614:J614"/>
     <mergeCell ref="B213:J213"/>
+    <mergeCell ref="B480:K480"/>
+    <mergeCell ref="B250:K250"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B149:J149"/>
+    <mergeCell ref="B215:J215"/>
+    <mergeCell ref="B289:K289"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B539:J539"/>
+    <mergeCell ref="B322:J322"/>
     <mergeCell ref="B497:J497"/>
     <mergeCell ref="B418:J418"/>
-    <mergeCell ref="B549:J549"/>
-    <mergeCell ref="B306:J306"/>
-    <mergeCell ref="B508:K508"/>
-    <mergeCell ref="B229:K229"/>
-    <mergeCell ref="B194:J194"/>
-    <mergeCell ref="B349:K349"/>
-    <mergeCell ref="B214:J214"/>
-    <mergeCell ref="B476:K476"/>
-    <mergeCell ref="B210:J210"/>
-    <mergeCell ref="B364:K364"/>
-    <mergeCell ref="B373:K373"/>
-    <mergeCell ref="B567:J567"/>
-    <mergeCell ref="B478:K478"/>
-    <mergeCell ref="B536:K536"/>
-    <mergeCell ref="B437:J437"/>
-    <mergeCell ref="B342:J342"/>
-    <mergeCell ref="B277:K277"/>
-    <mergeCell ref="B479:K479"/>
-    <mergeCell ref="B375:J375"/>
-    <mergeCell ref="B595:J595"/>
-    <mergeCell ref="B521:J521"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B593:K593"/>
-    <mergeCell ref="B304:K304"/>
-    <mergeCell ref="B372:K372"/>
-    <mergeCell ref="B157:J157"/>
-    <mergeCell ref="B320:I320"/>
-    <mergeCell ref="B359:K359"/>
-    <mergeCell ref="B251:K251"/>
-    <mergeCell ref="B296:K296"/>
-    <mergeCell ref="B361:K361"/>
-    <mergeCell ref="B218:K218"/>
-    <mergeCell ref="B158:J158"/>
-    <mergeCell ref="B486:J486"/>
-    <mergeCell ref="B121:J121"/>
-    <mergeCell ref="B148:J148"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="B189:J189"/>
-    <mergeCell ref="B585:J585"/>
-    <mergeCell ref="B188:J188"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B362:K362"/>
-    <mergeCell ref="B150:J150"/>
-    <mergeCell ref="B190:J190"/>
-    <mergeCell ref="B456:J456"/>
-    <mergeCell ref="B483:K483"/>
     <mergeCell ref="B177:J177"/>
-    <mergeCell ref="B291:K291"/>
-    <mergeCell ref="B475:K475"/>
-    <mergeCell ref="B511:J511"/>
     <mergeCell ref="B63:J63"/>
-    <mergeCell ref="B219:K219"/>
-    <mergeCell ref="B212:J212"/>
-    <mergeCell ref="B259:K259"/>
-    <mergeCell ref="B206:J206"/>
-    <mergeCell ref="B293:K293"/>
-    <mergeCell ref="B209:J209"/>
     <mergeCell ref="B140:J140"/>
-    <mergeCell ref="B267:K267"/>
-    <mergeCell ref="B202:J202"/>
-    <mergeCell ref="B290:K290"/>
-    <mergeCell ref="B367:K367"/>
     <mergeCell ref="B96:J96"/>
     <mergeCell ref="B152:J152"/>
-    <mergeCell ref="B288:K288"/>
-    <mergeCell ref="B332:J332"/>
-    <mergeCell ref="B253:K253"/>
-    <mergeCell ref="B287:K287"/>
-    <mergeCell ref="B230:K230"/>
     <mergeCell ref="B151:J151"/>
-    <mergeCell ref="B257:K257"/>
-    <mergeCell ref="B254:K254"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B241:K241"/>
-    <mergeCell ref="B256:K256"/>
-    <mergeCell ref="B369:K369"/>
-    <mergeCell ref="B191:J191"/>
-    <mergeCell ref="B205:J205"/>
-    <mergeCell ref="B368:K368"/>
-    <mergeCell ref="B211:J211"/>
-    <mergeCell ref="B358:K358"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16354,29 +16354,29 @@
       <c r="G1" s="180"/>
     </row>
     <row r="3" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="181" t="s">
+      <c r="B3" s="183" t="s">
         <v>638</v>
       </c>
       <c r="C3" s="182"/>
-      <c r="D3" s="181" t="s">
+      <c r="D3" s="183" t="s">
         <v>639</v>
       </c>
       <c r="E3" s="182"/>
-      <c r="F3" s="181" t="s">
+      <c r="F3" s="183" t="s">
         <v>640</v>
       </c>
       <c r="G3" s="182"/>
     </row>
     <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="183">
+      <c r="B4" s="181">
         <v>37245.760000000002</v>
       </c>
       <c r="C4" s="182"/>
-      <c r="D4" s="183">
+      <c r="D4" s="181">
         <v>6207.626666666667</v>
       </c>
       <c r="E4" s="182"/>
-      <c r="F4" s="183">
+      <c r="F4" s="181">
         <v>27488.73</v>
       </c>
       <c r="G4" s="182"/>
@@ -18183,6 +18183,7 @@
   </sheetData>
   <autoFilter ref="B33:G102" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="10">
+    <mergeCell ref="B1:G1"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D3:E3"/>
@@ -18192,7 +18193,6 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18212,7 +18212,8 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18229,37 +18230,37 @@
       <c r="I1" s="180"/>
     </row>
     <row r="3" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="181" t="s">
+      <c r="B3" s="183" t="s">
         <v>753</v>
       </c>
       <c r="C3" s="182"/>
-      <c r="D3" s="181" t="s">
+      <c r="D3" s="183" t="s">
         <v>754</v>
       </c>
       <c r="E3" s="182"/>
-      <c r="F3" s="181" t="s">
+      <c r="F3" s="183" t="s">
         <v>755</v>
       </c>
       <c r="G3" s="182"/>
-      <c r="H3" s="181" t="s">
+      <c r="H3" s="183" t="s">
         <v>756</v>
       </c>
       <c r="I3" s="182"/>
     </row>
     <row r="4" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="183">
+      <c r="B4" s="181">
         <v>0</v>
       </c>
       <c r="C4" s="182"/>
-      <c r="D4" s="183">
+      <c r="D4" s="181">
         <v>0</v>
       </c>
       <c r="E4" s="182"/>
-      <c r="F4" s="183">
+      <c r="F4" s="181">
         <v>0</v>
       </c>
       <c r="G4" s="182"/>
-      <c r="H4" s="183">
+      <c r="H4" s="181">
         <v>0</v>
       </c>
       <c r="I4" s="182"/>
@@ -18785,43 +18786,46 @@
       <c r="I29" s="177"/>
     </row>
     <row r="30" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="181" t="s">
+      <c r="B30" s="183" t="s">
         <v>781</v>
       </c>
       <c r="C30" s="182"/>
-      <c r="D30" s="181" t="s">
+      <c r="D30" s="183" t="s">
         <v>782</v>
       </c>
       <c r="E30" s="182"/>
-      <c r="F30" s="181" t="s">
+      <c r="F30" s="183" t="s">
         <v>783</v>
       </c>
       <c r="G30" s="182"/>
-      <c r="H30" s="181" t="s">
+      <c r="H30" s="183" t="s">
         <v>784</v>
       </c>
       <c r="I30" s="182"/>
     </row>
     <row r="31" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="184">
+      <c r="B31" s="185">
         <v>0</v>
       </c>
       <c r="C31" s="182"/>
-      <c r="D31" s="185">
+      <c r="D31" s="186">
         <v>0</v>
       </c>
       <c r="E31" s="182"/>
-      <c r="F31" s="186">
+      <c r="F31" s="184">
         <v>0</v>
       </c>
       <c r="G31" s="182"/>
-      <c r="H31" s="183">
+      <c r="H31" s="181">
         <v>0</v>
       </c>
       <c r="I31" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="F31:G31"/>
@@ -18838,9 +18842,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18870,13 +18871,13 @@
       <c r="F1" s="180"/>
     </row>
     <row r="3" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D3" s="181" t="s">
+      <c r="D3" s="183" t="s">
         <v>786</v>
       </c>
       <c r="E3" s="182"/>
     </row>
     <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D4" s="183">
+      <c r="D4" s="181">
         <v>45862.41</v>
       </c>
       <c r="E4" s="182"/>
